--- a/ID7010_E22.xlsx
+++ b/ID7010_E22.xlsx
@@ -1174,7 +1174,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1271,6 +1271,11 @@
       <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1475,9 +1480,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1518,6 +1520,9 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="15">
     <cellStyle name="60% - Accent1 2" xfId="1"/>
@@ -1810,13 +1815,13 @@
   <dimension ref="A1:F231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="39" style="28" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="28" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="28" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="39" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="28"/>
+    <col min="1" max="1" width="12.85546875" style="27" customWidth="1"/>
+    <col min="2" max="2" width="39" style="27" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="27" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="38" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1">
@@ -1849,29 +1854,33 @@
       <c r="C2" s="4">
         <v>95</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="25">
+      <c r="D2" s="41">
+        <v>75</v>
+      </c>
+      <c r="E2" s="24">
         <v>56</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="39">
         <v>47.620000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="24">
         <v>78</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25">
+      <c r="D3" s="41">
+        <v>84</v>
+      </c>
+      <c r="E3" s="24">
         <v>70</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -1882,14 +1891,16 @@
       <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="24">
         <v>85</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25">
+      <c r="D4" s="41">
+        <v>84</v>
+      </c>
+      <c r="E4" s="24">
         <v>76</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="39">
         <v>23.810000000000002</v>
       </c>
     </row>
@@ -1900,14 +1911,16 @@
       <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="24">
         <v>97</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25">
+      <c r="D5" s="41">
+        <v>89</v>
+      </c>
+      <c r="E5" s="24">
         <v>90</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -1918,14 +1931,16 @@
       <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>87</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25">
+      <c r="D6" s="41">
+        <v>89</v>
+      </c>
+      <c r="E6" s="24">
         <v>63</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -1936,14 +1951,16 @@
       <c r="B7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>68</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25">
+      <c r="D7" s="41">
+        <v>84</v>
+      </c>
+      <c r="E7" s="24">
         <v>48</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="39">
         <v>61.9</v>
       </c>
     </row>
@@ -1954,14 +1971,16 @@
       <c r="B8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="25">
-        <v>80</v>
-      </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25">
+      <c r="C8" s="24">
+        <v>80</v>
+      </c>
+      <c r="D8" s="41">
+        <v>74</v>
+      </c>
+      <c r="E8" s="24">
         <v>83</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -1972,14 +1991,16 @@
       <c r="B9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <v>98</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25">
+      <c r="D9" s="41">
+        <v>75</v>
+      </c>
+      <c r="E9" s="24">
         <v>82</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -1990,14 +2011,16 @@
       <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="24">
         <v>89</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25">
+      <c r="D10" s="41">
+        <v>74</v>
+      </c>
+      <c r="E10" s="24">
         <v>73</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2008,14 +2031,16 @@
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <v>96</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25">
+      <c r="D11" s="41">
+        <v>89</v>
+      </c>
+      <c r="E11" s="24">
         <v>82</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2026,14 +2051,16 @@
       <c r="B12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="24">
         <v>85</v>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25">
+      <c r="D12" s="41">
+        <v>82</v>
+      </c>
+      <c r="E12" s="24">
         <v>84</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2044,14 +2071,16 @@
       <c r="B13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>85</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="25">
+      <c r="D13" s="41">
+        <v>82</v>
+      </c>
+      <c r="E13" s="24">
         <v>81</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="39">
         <v>100</v>
       </c>
     </row>
@@ -2062,14 +2091,16 @@
       <c r="B14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>96</v>
       </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="25">
+      <c r="D14" s="41">
+        <v>80</v>
+      </c>
+      <c r="E14" s="24">
         <v>66</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="39">
         <v>100</v>
       </c>
     </row>
@@ -2080,14 +2111,16 @@
       <c r="B15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>85</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="25">
+      <c r="D15" s="41">
+        <v>82</v>
+      </c>
+      <c r="E15" s="24">
         <v>87</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2098,14 +2131,16 @@
       <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>82</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="25">
+      <c r="D16" s="41">
+        <v>78</v>
+      </c>
+      <c r="E16" s="24">
         <v>79</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2116,14 +2151,16 @@
       <c r="B17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>85</v>
       </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="25">
+      <c r="D17" s="41">
+        <v>72</v>
+      </c>
+      <c r="E17" s="24">
         <v>84</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2134,14 +2171,16 @@
       <c r="B18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="24">
         <v>88</v>
       </c>
-      <c r="D18" s="24"/>
-      <c r="E18" s="25">
+      <c r="D18" s="41">
+        <v>86</v>
+      </c>
+      <c r="E18" s="24">
         <v>83</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2152,14 +2191,16 @@
       <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="25">
-        <v>80</v>
-      </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="25">
+      <c r="C19" s="24">
+        <v>80</v>
+      </c>
+      <c r="D19" s="41">
+        <v>81</v>
+      </c>
+      <c r="E19" s="24">
         <v>88</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2170,14 +2211,16 @@
       <c r="B20" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>85</v>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="25">
-        <v>80</v>
-      </c>
-      <c r="F20" s="40">
+      <c r="D20" s="41">
+        <v>81</v>
+      </c>
+      <c r="E20" s="24">
+        <v>80</v>
+      </c>
+      <c r="F20" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -2188,14 +2231,16 @@
       <c r="B21" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>94</v>
       </c>
-      <c r="D21" s="24"/>
-      <c r="E21" s="25">
+      <c r="D21" s="41">
+        <v>86</v>
+      </c>
+      <c r="E21" s="24">
         <v>74</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -2206,14 +2251,16 @@
       <c r="B22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="24">
         <v>89</v>
       </c>
-      <c r="D22" s="24"/>
-      <c r="E22" s="25">
+      <c r="D22" s="41">
+        <v>82</v>
+      </c>
+      <c r="E22" s="24">
         <v>91</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2224,14 +2271,16 @@
       <c r="B23" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="24">
         <v>73</v>
       </c>
-      <c r="D23" s="24"/>
-      <c r="E23" s="25">
-        <v>80</v>
-      </c>
-      <c r="F23" s="40">
+      <c r="D23" s="41">
+        <v>82</v>
+      </c>
+      <c r="E23" s="24">
+        <v>80</v>
+      </c>
+      <c r="F23" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -2242,14 +2291,16 @@
       <c r="B24" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="25">
-        <v>80</v>
-      </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="25">
+      <c r="C24" s="24">
+        <v>80</v>
+      </c>
+      <c r="D24" s="41">
+        <v>75</v>
+      </c>
+      <c r="E24" s="24">
         <v>85</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2260,14 +2311,16 @@
       <c r="B25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="24">
         <v>78</v>
       </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="25">
+      <c r="D25" s="41">
+        <v>78</v>
+      </c>
+      <c r="E25" s="24">
         <v>84</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2278,14 +2331,16 @@
       <c r="B26" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="24">
         <v>85</v>
       </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="25">
+      <c r="D26" s="41">
+        <v>74</v>
+      </c>
+      <c r="E26" s="24">
         <v>82</v>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2296,14 +2351,16 @@
       <c r="B27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="24">
         <v>94</v>
       </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="25">
+      <c r="D27" s="41">
+        <v>72</v>
+      </c>
+      <c r="E27" s="24">
         <v>83</v>
       </c>
-      <c r="F27" s="40">
+      <c r="F27" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2314,14 +2371,16 @@
       <c r="B28" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="24">
         <v>91</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="25">
+      <c r="D28" s="41">
+        <v>72</v>
+      </c>
+      <c r="E28" s="24">
         <v>79</v>
       </c>
-      <c r="F28" s="40">
+      <c r="F28" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2332,14 +2391,16 @@
       <c r="B29" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="24">
         <v>88</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="25">
+      <c r="D29" s="41">
+        <v>72</v>
+      </c>
+      <c r="E29" s="24">
         <v>79</v>
       </c>
-      <c r="F29" s="40">
+      <c r="F29" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2350,14 +2411,16 @@
       <c r="B30" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="24">
         <v>88</v>
       </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="25">
+      <c r="D30" s="41">
+        <v>75</v>
+      </c>
+      <c r="E30" s="24">
         <v>77</v>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2368,14 +2431,16 @@
       <c r="B31" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="24">
         <v>81</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="25">
+      <c r="D31" s="41">
+        <v>78</v>
+      </c>
+      <c r="E31" s="24">
         <v>70</v>
       </c>
-      <c r="F31" s="40">
+      <c r="F31" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2386,14 +2451,16 @@
       <c r="B32" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="25">
-        <v>80</v>
-      </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="25">
+      <c r="C32" s="24">
+        <v>80</v>
+      </c>
+      <c r="D32" s="41">
+        <v>79</v>
+      </c>
+      <c r="E32" s="24">
         <v>60</v>
       </c>
-      <c r="F32" s="40">
+      <c r="F32" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2404,14 +2471,16 @@
       <c r="B33" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="24">
         <v>81</v>
       </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="25">
+      <c r="D33" s="41">
+        <v>78</v>
+      </c>
+      <c r="E33" s="24">
         <v>84</v>
       </c>
-      <c r="F33" s="40">
+      <c r="F33" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2422,14 +2491,16 @@
       <c r="B34" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="25">
-        <v>80</v>
-      </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="25">
+      <c r="C34" s="24">
+        <v>80</v>
+      </c>
+      <c r="D34" s="41">
+        <v>82</v>
+      </c>
+      <c r="E34" s="24">
         <v>49</v>
       </c>
-      <c r="F34" s="40">
+      <c r="F34" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2440,14 +2511,16 @@
       <c r="B35" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="25">
-        <v>80</v>
-      </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="25">
+      <c r="C35" s="24">
+        <v>80</v>
+      </c>
+      <c r="D35" s="41">
+        <v>75</v>
+      </c>
+      <c r="E35" s="24">
         <v>67</v>
       </c>
-      <c r="F35" s="40">
+      <c r="F35" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2458,14 +2531,16 @@
       <c r="B36" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="25">
-        <v>80</v>
-      </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="25">
+      <c r="C36" s="24">
+        <v>80</v>
+      </c>
+      <c r="D36" s="41">
+        <v>72</v>
+      </c>
+      <c r="E36" s="24">
         <v>85</v>
       </c>
-      <c r="F36" s="40">
+      <c r="F36" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2476,14 +2551,16 @@
       <c r="B37" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="24">
         <v>88</v>
       </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="25">
+      <c r="D37" s="41">
+        <v>78</v>
+      </c>
+      <c r="E37" s="24">
         <v>79</v>
       </c>
-      <c r="F37" s="40">
+      <c r="F37" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2494,14 +2571,16 @@
       <c r="B38" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="24">
         <v>73</v>
       </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="25">
+      <c r="D38" s="41">
+        <v>82</v>
+      </c>
+      <c r="E38" s="24">
         <v>69</v>
       </c>
-      <c r="F38" s="40">
+      <c r="F38" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2512,14 +2591,16 @@
       <c r="B39" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="25">
-        <v>80</v>
-      </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="25">
+      <c r="C39" s="24">
+        <v>80</v>
+      </c>
+      <c r="D39" s="41">
+        <v>79</v>
+      </c>
+      <c r="E39" s="24">
         <v>76</v>
       </c>
-      <c r="F39" s="40">
+      <c r="F39" s="39">
         <v>100</v>
       </c>
     </row>
@@ -2530,14 +2611,16 @@
       <c r="B40" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="24">
         <v>89</v>
       </c>
-      <c r="D40" s="24"/>
-      <c r="E40" s="25">
+      <c r="D40" s="41">
+        <v>80</v>
+      </c>
+      <c r="E40" s="24">
         <v>70</v>
       </c>
-      <c r="F40" s="40">
+      <c r="F40" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2548,14 +2631,16 @@
       <c r="B41" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="24">
         <v>96</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="25">
+      <c r="D41" s="41">
+        <v>86</v>
+      </c>
+      <c r="E41" s="24">
         <v>85</v>
       </c>
-      <c r="F41" s="40">
+      <c r="F41" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2566,14 +2651,16 @@
       <c r="B42" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="24">
         <v>78</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="25">
+      <c r="D42" s="41">
+        <v>82</v>
+      </c>
+      <c r="E42" s="24">
         <v>75</v>
       </c>
-      <c r="F42" s="40">
+      <c r="F42" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2584,14 +2671,16 @@
       <c r="B43" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="24">
         <v>96</v>
       </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="25">
+      <c r="D43" s="41">
+        <v>86</v>
+      </c>
+      <c r="E43" s="24">
         <v>69</v>
       </c>
-      <c r="F43" s="40">
+      <c r="F43" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -2602,14 +2691,16 @@
       <c r="B44" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="25">
-        <v>80</v>
-      </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="25">
+      <c r="C44" s="24">
+        <v>80</v>
+      </c>
+      <c r="D44" s="41">
+        <v>75</v>
+      </c>
+      <c r="E44" s="24">
         <v>63</v>
       </c>
-      <c r="F44" s="40">
+      <c r="F44" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2620,14 +2711,16 @@
       <c r="B45" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="24">
         <v>91</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="25">
+      <c r="D45" s="41">
+        <v>72</v>
+      </c>
+      <c r="E45" s="24">
         <v>62</v>
       </c>
-      <c r="F45" s="40">
+      <c r="F45" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2638,14 +2731,16 @@
       <c r="B46" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="24">
         <v>84</v>
       </c>
-      <c r="D46" s="24"/>
-      <c r="E46" s="25">
+      <c r="D46" s="41">
+        <v>86</v>
+      </c>
+      <c r="E46" s="24">
         <v>81</v>
       </c>
-      <c r="F46" s="40">
+      <c r="F46" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2656,14 +2751,16 @@
       <c r="B47" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="24">
         <v>85</v>
       </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="25">
-        <v>80</v>
-      </c>
-      <c r="F47" s="40">
+      <c r="D47" s="41">
+        <v>72</v>
+      </c>
+      <c r="E47" s="24">
+        <v>80</v>
+      </c>
+      <c r="F47" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2674,14 +2771,16 @@
       <c r="B48" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="25">
-        <v>80</v>
-      </c>
-      <c r="D48" s="24"/>
-      <c r="E48" s="25">
+      <c r="C48" s="24">
+        <v>80</v>
+      </c>
+      <c r="D48" s="41">
+        <v>75</v>
+      </c>
+      <c r="E48" s="24">
         <v>77</v>
       </c>
-      <c r="F48" s="40">
+      <c r="F48" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2692,14 +2791,16 @@
       <c r="B49" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="24">
         <v>85</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="25">
+      <c r="D49" s="41">
+        <v>78</v>
+      </c>
+      <c r="E49" s="24">
         <v>88</v>
       </c>
-      <c r="F49" s="40">
+      <c r="F49" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2710,14 +2811,16 @@
       <c r="B50" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="24">
         <v>68</v>
       </c>
-      <c r="D50" s="24"/>
-      <c r="E50" s="25">
+      <c r="D50" s="41">
+        <v>82</v>
+      </c>
+      <c r="E50" s="24">
         <v>85</v>
       </c>
-      <c r="F50" s="40">
+      <c r="F50" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2728,14 +2831,16 @@
       <c r="B51" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="25">
-        <v>80</v>
-      </c>
-      <c r="D51" s="24"/>
-      <c r="E51" s="25">
+      <c r="C51" s="24">
+        <v>80</v>
+      </c>
+      <c r="D51" s="41">
+        <v>72</v>
+      </c>
+      <c r="E51" s="24">
         <v>48</v>
       </c>
-      <c r="F51" s="40">
+      <c r="F51" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2746,14 +2851,16 @@
       <c r="B52" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="25">
-        <v>80</v>
-      </c>
-      <c r="D52" s="24"/>
-      <c r="E52" s="25">
+      <c r="C52" s="24">
+        <v>80</v>
+      </c>
+      <c r="D52" s="41">
+        <v>79</v>
+      </c>
+      <c r="E52" s="24">
         <v>78</v>
       </c>
-      <c r="F52" s="40">
+      <c r="F52" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2764,14 +2871,16 @@
       <c r="B53" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="24">
         <v>90</v>
       </c>
-      <c r="D53" s="24"/>
-      <c r="E53" s="25">
-        <v>80</v>
-      </c>
-      <c r="F53" s="40">
+      <c r="D53" s="41">
+        <v>72</v>
+      </c>
+      <c r="E53" s="24">
+        <v>80</v>
+      </c>
+      <c r="F53" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2782,14 +2891,16 @@
       <c r="B54" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="24">
         <v>85</v>
       </c>
-      <c r="D54" s="24"/>
-      <c r="E54" s="25">
+      <c r="D54" s="41">
+        <v>74</v>
+      </c>
+      <c r="E54" s="24">
         <v>56</v>
       </c>
-      <c r="F54" s="40">
+      <c r="F54" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2800,14 +2911,16 @@
       <c r="B55" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="24">
         <v>85</v>
       </c>
-      <c r="D55" s="24"/>
-      <c r="E55" s="25">
+      <c r="D55" s="41">
+        <v>62</v>
+      </c>
+      <c r="E55" s="24">
         <v>81</v>
       </c>
-      <c r="F55" s="40">
+      <c r="F55" s="39">
         <v>66.67</v>
       </c>
     </row>
@@ -2818,14 +2931,16 @@
       <c r="B56" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="25">
-        <v>80</v>
-      </c>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25">
+      <c r="C56" s="24">
+        <v>80</v>
+      </c>
+      <c r="D56" s="41">
+        <v>62</v>
+      </c>
+      <c r="E56" s="24">
         <v>75</v>
       </c>
-      <c r="F56" s="40">
+      <c r="F56" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2836,14 +2951,16 @@
       <c r="B57" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="24">
         <v>85</v>
       </c>
-      <c r="D57" s="24"/>
-      <c r="E57" s="25">
+      <c r="D57" s="41">
+        <v>75</v>
+      </c>
+      <c r="E57" s="24">
         <v>82</v>
       </c>
-      <c r="F57" s="40">
+      <c r="F57" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2854,14 +2971,16 @@
       <c r="B58" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="25">
-        <v>80</v>
-      </c>
-      <c r="D58" s="24"/>
-      <c r="E58" s="25">
+      <c r="C58" s="24">
+        <v>80</v>
+      </c>
+      <c r="D58" s="41">
+        <v>72</v>
+      </c>
+      <c r="E58" s="24">
         <v>70</v>
       </c>
-      <c r="F58" s="40">
+      <c r="F58" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2872,32 +2991,36 @@
       <c r="B59" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="24">
         <v>86</v>
       </c>
-      <c r="D59" s="24"/>
-      <c r="E59" s="25">
-        <v>80</v>
-      </c>
-      <c r="F59" s="40">
+      <c r="D59" s="41">
+        <v>89</v>
+      </c>
+      <c r="E59" s="24">
+        <v>80</v>
+      </c>
+      <c r="F59" s="39">
         <v>85.71</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="27" t="s">
+      <c r="A60" s="26" t="s">
         <v>122</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="25">
+      <c r="C60" s="24">
         <v>85</v>
       </c>
-      <c r="D60" s="24"/>
-      <c r="E60" s="25">
+      <c r="D60" s="41">
         <v>81</v>
       </c>
-      <c r="F60" s="40">
+      <c r="E60" s="24">
+        <v>81</v>
+      </c>
+      <c r="F60" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2908,14 +3031,16 @@
       <c r="B61" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="24">
         <v>86</v>
       </c>
-      <c r="D61" s="24"/>
-      <c r="E61" s="25">
+      <c r="D61" s="41">
+        <v>89</v>
+      </c>
+      <c r="E61" s="24">
         <v>71</v>
       </c>
-      <c r="F61" s="40">
+      <c r="F61" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2926,14 +3051,16 @@
       <c r="B62" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C62" s="25">
+      <c r="C62" s="24">
         <v>92</v>
       </c>
-      <c r="D62" s="24"/>
-      <c r="E62" s="25">
+      <c r="D62" s="41">
+        <v>75</v>
+      </c>
+      <c r="E62" s="24">
         <v>81</v>
       </c>
-      <c r="F62" s="40">
+      <c r="F62" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2944,14 +3071,16 @@
       <c r="B63" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C63" s="25">
+      <c r="C63" s="24">
         <v>85</v>
       </c>
-      <c r="D63" s="24"/>
-      <c r="E63" s="25">
+      <c r="D63" s="41">
+        <v>84</v>
+      </c>
+      <c r="E63" s="24">
         <v>74</v>
       </c>
-      <c r="F63" s="40">
+      <c r="F63" s="39">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -2962,14 +3091,16 @@
       <c r="B64" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C64" s="25">
-        <v>80</v>
-      </c>
-      <c r="D64" s="24"/>
-      <c r="E64" s="25">
+      <c r="C64" s="24">
+        <v>80</v>
+      </c>
+      <c r="D64" s="41">
+        <v>75</v>
+      </c>
+      <c r="E64" s="24">
         <v>78</v>
       </c>
-      <c r="F64" s="40">
+      <c r="F64" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -2980,14 +3111,16 @@
       <c r="B65" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="25">
+      <c r="C65" s="24">
         <v>75</v>
       </c>
-      <c r="D65" s="24"/>
-      <c r="E65" s="25">
+      <c r="D65" s="41">
+        <v>85</v>
+      </c>
+      <c r="E65" s="24">
         <v>51</v>
       </c>
-      <c r="F65" s="40">
+      <c r="F65" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -2998,14 +3131,16 @@
       <c r="B66" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C66" s="25">
+      <c r="C66" s="24">
         <v>90</v>
       </c>
-      <c r="D66" s="24"/>
-      <c r="E66" s="25">
+      <c r="D66" s="41">
+        <v>89</v>
+      </c>
+      <c r="E66" s="24">
         <v>50</v>
       </c>
-      <c r="F66" s="40">
+      <c r="F66" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3016,14 +3151,16 @@
       <c r="B67" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C67" s="25">
+      <c r="C67" s="24">
         <v>93</v>
       </c>
-      <c r="D67" s="24"/>
-      <c r="E67" s="25">
+      <c r="D67" s="41">
+        <v>79</v>
+      </c>
+      <c r="E67" s="24">
         <v>78</v>
       </c>
-      <c r="F67" s="40">
+      <c r="F67" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3034,14 +3171,16 @@
       <c r="B68" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="24">
         <v>86</v>
       </c>
-      <c r="D68" s="24"/>
-      <c r="E68" s="25">
+      <c r="D68" s="41">
+        <v>89</v>
+      </c>
+      <c r="E68" s="24">
         <v>73</v>
       </c>
-      <c r="F68" s="40">
+      <c r="F68" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3052,14 +3191,16 @@
       <c r="B69" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C69" s="25">
+      <c r="C69" s="24">
         <v>93</v>
       </c>
-      <c r="D69" s="24"/>
-      <c r="E69" s="25">
+      <c r="D69" s="41">
+        <v>62</v>
+      </c>
+      <c r="E69" s="24">
         <v>63</v>
       </c>
-      <c r="F69" s="40">
+      <c r="F69" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3070,14 +3211,16 @@
       <c r="B70" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C70" s="25">
-        <v>80</v>
-      </c>
-      <c r="D70" s="24"/>
-      <c r="E70" s="25">
+      <c r="C70" s="24">
+        <v>80</v>
+      </c>
+      <c r="D70" s="41">
+        <v>79</v>
+      </c>
+      <c r="E70" s="24">
         <v>83</v>
       </c>
-      <c r="F70" s="40">
+      <c r="F70" s="39">
         <v>100</v>
       </c>
     </row>
@@ -3088,14 +3231,16 @@
       <c r="B71" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="24">
         <v>97</v>
       </c>
-      <c r="D71" s="24"/>
-      <c r="E71" s="25">
+      <c r="D71" s="41">
+        <v>86</v>
+      </c>
+      <c r="E71" s="24">
         <v>83</v>
       </c>
-      <c r="F71" s="40">
+      <c r="F71" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3106,14 +3251,16 @@
       <c r="B72" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C72" s="25">
-        <v>80</v>
-      </c>
-      <c r="D72" s="24"/>
-      <c r="E72" s="25">
+      <c r="C72" s="24">
+        <v>80</v>
+      </c>
+      <c r="D72" s="41">
+        <v>81</v>
+      </c>
+      <c r="E72" s="24">
         <v>65</v>
       </c>
-      <c r="F72" s="40">
+      <c r="F72" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3124,14 +3271,16 @@
       <c r="B73" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C73" s="25">
+      <c r="C73" s="24">
         <v>86</v>
       </c>
-      <c r="D73" s="24"/>
-      <c r="E73" s="25">
+      <c r="D73" s="41">
+        <v>78</v>
+      </c>
+      <c r="E73" s="24">
         <v>87</v>
       </c>
-      <c r="F73" s="40">
+      <c r="F73" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3142,14 +3291,16 @@
       <c r="B74" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="C74" s="25">
+      <c r="C74" s="24">
         <v>85</v>
       </c>
-      <c r="D74" s="24"/>
-      <c r="E74" s="25">
+      <c r="D74" s="41">
+        <v>80</v>
+      </c>
+      <c r="E74" s="24">
         <v>85</v>
       </c>
-      <c r="F74" s="40">
+      <c r="F74" s="39">
         <v>100</v>
       </c>
     </row>
@@ -3160,14 +3311,16 @@
       <c r="B75" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C75" s="25">
+      <c r="C75" s="24">
         <v>93</v>
       </c>
-      <c r="D75" s="24"/>
-      <c r="E75" s="25">
+      <c r="D75" s="41">
+        <v>82</v>
+      </c>
+      <c r="E75" s="24">
         <v>90</v>
       </c>
-      <c r="F75" s="40">
+      <c r="F75" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3178,14 +3331,16 @@
       <c r="B76" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C76" s="25">
+      <c r="C76" s="24">
         <v>85</v>
       </c>
-      <c r="D76" s="24"/>
-      <c r="E76" s="25">
+      <c r="D76" s="41">
+        <v>80</v>
+      </c>
+      <c r="E76" s="24">
         <v>87</v>
       </c>
-      <c r="F76" s="40">
+      <c r="F76" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3196,14 +3351,16 @@
       <c r="B77" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C77" s="25">
+      <c r="C77" s="24">
         <v>95</v>
       </c>
-      <c r="D77" s="24"/>
-      <c r="E77" s="25">
-        <v>80</v>
-      </c>
-      <c r="F77" s="40">
+      <c r="D77" s="41">
+        <v>89</v>
+      </c>
+      <c r="E77" s="24">
+        <v>80</v>
+      </c>
+      <c r="F77" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3214,14 +3371,16 @@
       <c r="B78" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C78" s="25">
+      <c r="C78" s="24">
         <v>90</v>
       </c>
-      <c r="D78" s="24"/>
-      <c r="E78" s="25">
+      <c r="D78" s="41">
+        <v>80</v>
+      </c>
+      <c r="E78" s="24">
         <v>76</v>
       </c>
-      <c r="F78" s="40">
+      <c r="F78" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -3232,14 +3391,16 @@
       <c r="B79" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C79" s="25">
-        <v>80</v>
-      </c>
-      <c r="D79" s="24"/>
-      <c r="E79" s="25">
+      <c r="C79" s="24">
+        <v>80</v>
+      </c>
+      <c r="D79" s="41">
+        <v>72</v>
+      </c>
+      <c r="E79" s="24">
         <v>85</v>
       </c>
-      <c r="F79" s="40">
+      <c r="F79" s="39">
         <v>100</v>
       </c>
     </row>
@@ -3250,14 +3411,16 @@
       <c r="B80" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C80" s="25">
+      <c r="C80" s="24">
         <v>95</v>
       </c>
-      <c r="D80" s="24"/>
-      <c r="E80" s="25">
+      <c r="D80" s="41">
+        <v>79</v>
+      </c>
+      <c r="E80" s="24">
         <v>87</v>
       </c>
-      <c r="F80" s="40">
+      <c r="F80" s="39">
         <v>100</v>
       </c>
     </row>
@@ -3268,14 +3431,16 @@
       <c r="B81" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C81" s="25">
+      <c r="C81" s="24">
         <v>89</v>
       </c>
-      <c r="D81" s="24"/>
-      <c r="E81" s="25">
+      <c r="D81" s="41">
+        <v>78</v>
+      </c>
+      <c r="E81" s="24">
         <v>84</v>
       </c>
-      <c r="F81" s="40">
+      <c r="F81" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3286,14 +3451,16 @@
       <c r="B82" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C82" s="25">
+      <c r="C82" s="24">
         <v>87</v>
       </c>
-      <c r="D82" s="24"/>
-      <c r="E82" s="25">
+      <c r="D82" s="41">
+        <v>84</v>
+      </c>
+      <c r="E82" s="24">
         <v>60</v>
       </c>
-      <c r="F82" s="40">
+      <c r="F82" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -3304,14 +3471,16 @@
       <c r="B83" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C83" s="25">
+      <c r="C83" s="24">
         <v>87</v>
       </c>
-      <c r="D83" s="24"/>
-      <c r="E83" s="25">
+      <c r="D83" s="41">
+        <v>82</v>
+      </c>
+      <c r="E83" s="24">
         <v>69</v>
       </c>
-      <c r="F83" s="40">
+      <c r="F83" s="39">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -3322,14 +3491,16 @@
       <c r="B84" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C84" s="25">
-        <v>80</v>
-      </c>
-      <c r="D84" s="24"/>
-      <c r="E84" s="25">
+      <c r="C84" s="24">
+        <v>80</v>
+      </c>
+      <c r="D84" s="41">
+        <v>84</v>
+      </c>
+      <c r="E84" s="24">
         <v>85</v>
       </c>
-      <c r="F84" s="40">
+      <c r="F84" s="39">
         <v>66.67</v>
       </c>
     </row>
@@ -3340,14 +3511,16 @@
       <c r="B85" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C85" s="25">
+      <c r="C85" s="24">
         <v>85</v>
       </c>
-      <c r="D85" s="24"/>
-      <c r="E85" s="25">
+      <c r="D85" s="41">
+        <v>84</v>
+      </c>
+      <c r="E85" s="24">
         <v>78</v>
       </c>
-      <c r="F85" s="40">
+      <c r="F85" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3358,14 +3531,16 @@
       <c r="B86" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C86" s="25">
+      <c r="C86" s="24">
         <v>88</v>
       </c>
-      <c r="D86" s="24"/>
-      <c r="E86" s="25">
+      <c r="D86" s="41">
+        <v>82</v>
+      </c>
+      <c r="E86" s="24">
         <v>83</v>
       </c>
-      <c r="F86" s="40">
+      <c r="F86" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3376,14 +3551,16 @@
       <c r="B87" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C87" s="25">
+      <c r="C87" s="24">
         <v>91</v>
       </c>
-      <c r="D87" s="24"/>
-      <c r="E87" s="25">
+      <c r="D87" s="41">
+        <v>84</v>
+      </c>
+      <c r="E87" s="24">
         <v>51</v>
       </c>
-      <c r="F87" s="40">
+      <c r="F87" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3394,14 +3571,16 @@
       <c r="B88" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C88" s="25">
+      <c r="C88" s="24">
         <v>87</v>
       </c>
-      <c r="D88" s="24"/>
-      <c r="E88" s="25">
+      <c r="D88" s="41">
+        <v>89</v>
+      </c>
+      <c r="E88" s="24">
         <v>68</v>
       </c>
-      <c r="F88" s="40">
+      <c r="F88" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3412,14 +3591,16 @@
       <c r="B89" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C89" s="25">
+      <c r="C89" s="24">
         <v>85</v>
       </c>
-      <c r="D89" s="24"/>
-      <c r="E89" s="25">
+      <c r="D89" s="41">
+        <v>78</v>
+      </c>
+      <c r="E89" s="24">
         <v>83</v>
       </c>
-      <c r="F89" s="40">
+      <c r="F89" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3430,14 +3611,16 @@
       <c r="B90" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C90" s="25">
+      <c r="C90" s="24">
         <v>75</v>
       </c>
-      <c r="D90" s="24"/>
-      <c r="E90" s="25">
+      <c r="D90" s="41">
+        <v>85</v>
+      </c>
+      <c r="E90" s="24">
         <v>81</v>
       </c>
-      <c r="F90" s="40">
+      <c r="F90" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3448,14 +3631,16 @@
       <c r="B91" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C91" s="25">
+      <c r="C91" s="24">
         <v>83</v>
       </c>
-      <c r="D91" s="24"/>
-      <c r="E91" s="25">
+      <c r="D91" s="41">
+        <v>85</v>
+      </c>
+      <c r="E91" s="24">
         <v>84</v>
       </c>
-      <c r="F91" s="40">
+      <c r="F91" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3466,14 +3651,16 @@
       <c r="B92" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C92" s="25">
+      <c r="C92" s="24">
         <v>96</v>
       </c>
-      <c r="D92" s="24"/>
-      <c r="E92" s="25">
+      <c r="D92" s="41">
+        <v>80</v>
+      </c>
+      <c r="E92" s="24">
         <v>85</v>
       </c>
-      <c r="F92" s="40">
+      <c r="F92" s="39">
         <v>100</v>
       </c>
     </row>
@@ -3484,14 +3671,16 @@
       <c r="B93" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C93" s="25">
+      <c r="C93" s="24">
         <v>70</v>
       </c>
-      <c r="D93" s="24"/>
-      <c r="E93" s="25">
+      <c r="D93" s="41">
+        <v>82</v>
+      </c>
+      <c r="E93" s="24">
         <v>78</v>
       </c>
-      <c r="F93" s="40">
+      <c r="F93" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -3502,14 +3691,16 @@
       <c r="B94" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C94" s="25">
+      <c r="C94" s="24">
         <v>85</v>
       </c>
-      <c r="D94" s="24"/>
-      <c r="E94" s="25">
+      <c r="D94" s="41">
+        <v>78</v>
+      </c>
+      <c r="E94" s="24">
         <v>67</v>
       </c>
-      <c r="F94" s="40">
+      <c r="F94" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3520,14 +3711,16 @@
       <c r="B95" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C95" s="25">
-        <v>80</v>
-      </c>
-      <c r="D95" s="24"/>
-      <c r="E95" s="25">
+      <c r="C95" s="24">
+        <v>80</v>
+      </c>
+      <c r="D95" s="41">
+        <v>62</v>
+      </c>
+      <c r="E95" s="24">
         <v>75</v>
       </c>
-      <c r="F95" s="40">
+      <c r="F95" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3538,14 +3731,16 @@
       <c r="B96" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C96" s="25">
+      <c r="C96" s="24">
         <v>89</v>
       </c>
-      <c r="D96" s="24"/>
-      <c r="E96" s="25">
+      <c r="D96" s="41">
+        <v>85</v>
+      </c>
+      <c r="E96" s="24">
         <v>81</v>
       </c>
-      <c r="F96" s="40">
+      <c r="F96" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3556,14 +3751,16 @@
       <c r="B97" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C97" s="25">
+      <c r="C97" s="24">
         <v>85</v>
       </c>
-      <c r="D97" s="24"/>
-      <c r="E97" s="25">
+      <c r="D97" s="41">
+        <v>72</v>
+      </c>
+      <c r="E97" s="24">
         <v>67</v>
       </c>
-      <c r="F97" s="40">
+      <c r="F97" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3574,14 +3771,16 @@
       <c r="B98" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C98" s="25">
+      <c r="C98" s="24">
         <v>85</v>
       </c>
-      <c r="D98" s="24"/>
-      <c r="E98" s="25">
+      <c r="D98" s="41">
+        <v>81</v>
+      </c>
+      <c r="E98" s="24">
         <v>82</v>
       </c>
-      <c r="F98" s="40">
+      <c r="F98" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3592,14 +3791,16 @@
       <c r="B99" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C99" s="25">
+      <c r="C99" s="24">
         <v>88</v>
       </c>
-      <c r="D99" s="24"/>
-      <c r="E99" s="25">
+      <c r="D99" s="41">
+        <v>80</v>
+      </c>
+      <c r="E99" s="24">
         <v>87</v>
       </c>
-      <c r="F99" s="40">
+      <c r="F99" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3610,14 +3811,16 @@
       <c r="B100" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="C100" s="25">
+      <c r="C100" s="24">
         <v>87</v>
       </c>
-      <c r="D100" s="24"/>
-      <c r="E100" s="25">
+      <c r="D100" s="41">
+        <v>80</v>
+      </c>
+      <c r="E100" s="24">
         <v>87</v>
       </c>
-      <c r="F100" s="40">
+      <c r="F100" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3628,14 +3831,16 @@
       <c r="B101" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C101" s="25">
+      <c r="C101" s="24">
         <v>88</v>
       </c>
-      <c r="D101" s="24"/>
-      <c r="E101" s="25">
+      <c r="D101" s="41">
+        <v>82</v>
+      </c>
+      <c r="E101" s="24">
         <v>65</v>
       </c>
-      <c r="F101" s="40">
+      <c r="F101" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3646,14 +3851,16 @@
       <c r="B102" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C102" s="25">
+      <c r="C102" s="24">
         <v>94</v>
       </c>
-      <c r="D102" s="24"/>
-      <c r="E102" s="25">
+      <c r="D102" s="41">
+        <v>79</v>
+      </c>
+      <c r="E102" s="24">
         <v>72</v>
       </c>
-      <c r="F102" s="40">
+      <c r="F102" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3664,14 +3871,16 @@
       <c r="B103" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C103" s="25">
+      <c r="C103" s="24">
         <v>89</v>
       </c>
-      <c r="D103" s="24"/>
-      <c r="E103" s="25">
+      <c r="D103" s="41">
+        <v>72</v>
+      </c>
+      <c r="E103" s="24">
         <v>40</v>
       </c>
-      <c r="F103" s="40">
+      <c r="F103" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3682,14 +3891,16 @@
       <c r="B104" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C104" s="25">
+      <c r="C104" s="24">
         <v>88</v>
       </c>
-      <c r="D104" s="24"/>
-      <c r="E104" s="25">
+      <c r="D104" s="41">
+        <v>80</v>
+      </c>
+      <c r="E104" s="24">
         <v>55</v>
       </c>
-      <c r="F104" s="40">
+      <c r="F104" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3700,14 +3911,16 @@
       <c r="B105" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C105" s="25">
+      <c r="C105" s="24">
         <v>91</v>
       </c>
-      <c r="D105" s="24"/>
-      <c r="E105" s="25">
+      <c r="D105" s="41">
+        <v>82</v>
+      </c>
+      <c r="E105" s="24">
         <v>79</v>
       </c>
-      <c r="F105" s="40">
+      <c r="F105" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3718,14 +3931,16 @@
       <c r="B106" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C106" s="25">
+      <c r="C106" s="24">
         <v>90</v>
       </c>
-      <c r="D106" s="24"/>
-      <c r="E106" s="25">
+      <c r="D106" s="41">
+        <v>80</v>
+      </c>
+      <c r="E106" s="24">
         <v>44</v>
       </c>
-      <c r="F106" s="40">
+      <c r="F106" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3736,14 +3951,16 @@
       <c r="B107" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C107" s="25">
-        <v>80</v>
-      </c>
-      <c r="D107" s="24"/>
-      <c r="E107" s="25">
+      <c r="C107" s="24">
+        <v>80</v>
+      </c>
+      <c r="D107" s="41">
+        <v>75</v>
+      </c>
+      <c r="E107" s="24">
         <v>85</v>
       </c>
-      <c r="F107" s="40">
+      <c r="F107" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3754,14 +3971,16 @@
       <c r="B108" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C108" s="25">
+      <c r="C108" s="24">
         <v>71</v>
       </c>
-      <c r="D108" s="24"/>
-      <c r="E108" s="25">
+      <c r="D108" s="41">
+        <v>85</v>
+      </c>
+      <c r="E108" s="24">
         <v>70</v>
       </c>
-      <c r="F108" s="40">
+      <c r="F108" s="39">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -3772,14 +3991,16 @@
       <c r="B109" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C109" s="25">
+      <c r="C109" s="24">
         <v>95</v>
       </c>
-      <c r="D109" s="24"/>
-      <c r="E109" s="25">
+      <c r="D109" s="41">
+        <v>86</v>
+      </c>
+      <c r="E109" s="24">
         <v>76</v>
       </c>
-      <c r="F109" s="40">
+      <c r="F109" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3790,14 +4011,16 @@
       <c r="B110" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C110" s="25">
+      <c r="C110" s="24">
         <v>92</v>
       </c>
-      <c r="D110" s="24"/>
-      <c r="E110" s="25">
+      <c r="D110" s="41">
+        <v>86</v>
+      </c>
+      <c r="E110" s="24">
         <v>51</v>
       </c>
-      <c r="F110" s="40">
+      <c r="F110" s="39">
         <v>84.21</v>
       </c>
     </row>
@@ -3808,14 +4031,16 @@
       <c r="B111" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C111" s="25">
-        <v>80</v>
-      </c>
-      <c r="D111" s="24"/>
-      <c r="E111" s="25">
+      <c r="C111" s="24">
+        <v>80</v>
+      </c>
+      <c r="D111" s="41">
+        <v>75</v>
+      </c>
+      <c r="E111" s="24">
         <v>63</v>
       </c>
-      <c r="F111" s="40">
+      <c r="F111" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3826,14 +4051,16 @@
       <c r="B112" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C112" s="25">
+      <c r="C112" s="24">
         <v>85</v>
       </c>
-      <c r="D112" s="24"/>
-      <c r="E112" s="25">
+      <c r="D112" s="41">
+        <v>80</v>
+      </c>
+      <c r="E112" s="24">
         <v>72</v>
       </c>
-      <c r="F112" s="40">
+      <c r="F112" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3844,14 +4071,16 @@
       <c r="B113" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C113" s="25">
-        <v>80</v>
-      </c>
-      <c r="D113" s="24"/>
-      <c r="E113" s="25">
+      <c r="C113" s="24">
+        <v>80</v>
+      </c>
+      <c r="D113" s="41">
+        <v>72</v>
+      </c>
+      <c r="E113" s="24">
         <v>64</v>
       </c>
-      <c r="F113" s="40">
+      <c r="F113" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -3862,14 +4091,16 @@
       <c r="B114" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C114" s="25">
+      <c r="C114" s="24">
         <v>84</v>
       </c>
-      <c r="D114" s="24"/>
-      <c r="E114" s="25">
+      <c r="D114" s="41">
+        <v>81</v>
+      </c>
+      <c r="E114" s="24">
         <v>77</v>
       </c>
-      <c r="F114" s="40">
+      <c r="F114" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3880,14 +4111,16 @@
       <c r="B115" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C115" s="25">
+      <c r="C115" s="24">
         <v>89</v>
       </c>
-      <c r="D115" s="24"/>
-      <c r="E115" s="25">
+      <c r="D115" s="41">
+        <v>82</v>
+      </c>
+      <c r="E115" s="24">
         <v>69</v>
       </c>
-      <c r="F115" s="40">
+      <c r="F115" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -3898,14 +4131,16 @@
       <c r="B116" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="C116" s="25">
+      <c r="C116" s="24">
         <v>78</v>
       </c>
-      <c r="D116" s="24"/>
-      <c r="E116" s="25">
+      <c r="D116" s="41">
+        <v>80</v>
+      </c>
+      <c r="E116" s="24">
         <v>75</v>
       </c>
-      <c r="F116" s="40">
+      <c r="F116" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -3916,14 +4151,16 @@
       <c r="B117" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C117" s="25">
-        <v>80</v>
-      </c>
-      <c r="D117" s="24"/>
-      <c r="E117" s="25">
+      <c r="C117" s="24">
+        <v>80</v>
+      </c>
+      <c r="D117" s="41">
+        <v>82</v>
+      </c>
+      <c r="E117" s="24">
         <v>92</v>
       </c>
-      <c r="F117" s="40">
+      <c r="F117" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -3934,14 +4171,16 @@
       <c r="B118" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C118" s="25">
+      <c r="C118" s="24">
         <v>87</v>
       </c>
-      <c r="D118" s="24"/>
-      <c r="E118" s="25">
+      <c r="D118" s="41">
+        <v>84</v>
+      </c>
+      <c r="E118" s="24">
         <v>74</v>
       </c>
-      <c r="F118" s="40">
+      <c r="F118" s="39">
         <v>57.14</v>
       </c>
     </row>
@@ -3952,14 +4191,16 @@
       <c r="B119" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C119" s="25">
+      <c r="C119" s="24">
         <v>83</v>
       </c>
-      <c r="D119" s="24"/>
-      <c r="E119" s="25">
+      <c r="D119" s="41">
+        <v>72</v>
+      </c>
+      <c r="E119" s="24">
         <v>82</v>
       </c>
-      <c r="F119" s="40">
+      <c r="F119" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -3970,14 +4211,16 @@
       <c r="B120" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C120" s="25">
+      <c r="C120" s="24">
         <v>89</v>
       </c>
-      <c r="D120" s="24"/>
-      <c r="E120" s="25">
+      <c r="D120" s="41">
+        <v>75</v>
+      </c>
+      <c r="E120" s="24">
         <v>52</v>
       </c>
-      <c r="F120" s="40">
+      <c r="F120" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3988,14 +4231,16 @@
       <c r="B121" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C121" s="25">
+      <c r="C121" s="24">
         <v>94</v>
       </c>
-      <c r="D121" s="24"/>
-      <c r="E121" s="25">
-        <v>80</v>
-      </c>
-      <c r="F121" s="40">
+      <c r="D121" s="41">
+        <v>85</v>
+      </c>
+      <c r="E121" s="24">
+        <v>80</v>
+      </c>
+      <c r="F121" s="39">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -4006,14 +4251,16 @@
       <c r="B122" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C122" s="25">
-        <v>80</v>
-      </c>
-      <c r="D122" s="24"/>
-      <c r="E122" s="25">
+      <c r="C122" s="24">
+        <v>80</v>
+      </c>
+      <c r="D122" s="41">
+        <v>75</v>
+      </c>
+      <c r="E122" s="24">
         <v>33</v>
       </c>
-      <c r="F122" s="40">
+      <c r="F122" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -4024,14 +4271,16 @@
       <c r="B123" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="C123" s="25">
-        <v>80</v>
-      </c>
-      <c r="D123" s="24"/>
-      <c r="E123" s="25">
+      <c r="C123" s="24">
+        <v>80</v>
+      </c>
+      <c r="D123" s="41">
+        <v>82</v>
+      </c>
+      <c r="E123" s="24">
         <v>54</v>
       </c>
-      <c r="F123" s="40">
+      <c r="F123" s="39">
         <v>61.539999999999992</v>
       </c>
     </row>
@@ -4042,14 +4291,16 @@
       <c r="B124" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C124" s="25">
-        <v>80</v>
-      </c>
-      <c r="D124" s="24"/>
-      <c r="E124" s="25">
+      <c r="C124" s="24">
+        <v>80</v>
+      </c>
+      <c r="D124" s="41">
+        <v>75</v>
+      </c>
+      <c r="E124" s="24">
         <v>62</v>
       </c>
-      <c r="F124" s="40">
+      <c r="F124" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4060,14 +4311,16 @@
       <c r="B125" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C125" s="25">
+      <c r="C125" s="24">
         <v>85</v>
       </c>
-      <c r="D125" s="24"/>
-      <c r="E125" s="25">
+      <c r="D125" s="41">
+        <v>78</v>
+      </c>
+      <c r="E125" s="24">
         <v>62</v>
       </c>
-      <c r="F125" s="40">
+      <c r="F125" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4078,14 +4331,16 @@
       <c r="B126" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C126" s="25">
-        <v>80</v>
-      </c>
-      <c r="D126" s="24"/>
-      <c r="E126" s="25">
+      <c r="C126" s="24">
+        <v>80</v>
+      </c>
+      <c r="D126" s="41">
+        <v>78</v>
+      </c>
+      <c r="E126" s="24">
         <v>77</v>
       </c>
-      <c r="F126" s="40">
+      <c r="F126" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4096,14 +4351,16 @@
       <c r="B127" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C127" s="25">
+      <c r="C127" s="24">
         <v>88</v>
       </c>
-      <c r="D127" s="24"/>
-      <c r="E127" s="25">
+      <c r="D127" s="41">
+        <v>80</v>
+      </c>
+      <c r="E127" s="24">
         <v>62</v>
       </c>
-      <c r="F127" s="40">
+      <c r="F127" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4114,14 +4371,16 @@
       <c r="B128" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C128" s="25">
-        <v>80</v>
-      </c>
-      <c r="D128" s="24"/>
-      <c r="E128" s="25">
+      <c r="C128" s="24">
+        <v>80</v>
+      </c>
+      <c r="D128" s="41">
+        <v>82</v>
+      </c>
+      <c r="E128" s="24">
         <v>60</v>
       </c>
-      <c r="F128" s="40">
+      <c r="F128" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -4132,14 +4391,16 @@
       <c r="B129" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C129" s="25">
+      <c r="C129" s="24">
         <v>91</v>
       </c>
-      <c r="D129" s="24"/>
-      <c r="E129" s="25">
+      <c r="D129" s="41">
+        <v>74</v>
+      </c>
+      <c r="E129" s="24">
         <v>77</v>
       </c>
-      <c r="F129" s="40">
+      <c r="F129" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4150,14 +4411,16 @@
       <c r="B130" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="C130" s="25">
+      <c r="C130" s="24">
         <v>89</v>
       </c>
-      <c r="D130" s="24"/>
-      <c r="E130" s="25">
+      <c r="D130" s="41">
+        <v>78</v>
+      </c>
+      <c r="E130" s="24">
         <v>73</v>
       </c>
-      <c r="F130" s="40">
+      <c r="F130" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4168,14 +4431,16 @@
       <c r="B131" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="25">
+      <c r="C131" s="24">
         <v>88</v>
       </c>
-      <c r="D131" s="24"/>
-      <c r="E131" s="25">
+      <c r="D131" s="41">
+        <v>72</v>
+      </c>
+      <c r="E131" s="24">
         <v>48</v>
       </c>
-      <c r="F131" s="40">
+      <c r="F131" s="39">
         <v>61.9</v>
       </c>
     </row>
@@ -4186,14 +4451,16 @@
       <c r="B132" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="C132" s="25">
-        <v>80</v>
-      </c>
-      <c r="D132" s="24"/>
-      <c r="E132" s="25">
+      <c r="C132" s="24">
+        <v>80</v>
+      </c>
+      <c r="D132" s="41">
+        <v>75</v>
+      </c>
+      <c r="E132" s="24">
         <v>65</v>
       </c>
-      <c r="F132" s="40">
+      <c r="F132" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4204,14 +4471,16 @@
       <c r="B133" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="C133" s="25">
+      <c r="C133" s="24">
         <v>85</v>
       </c>
-      <c r="D133" s="24"/>
-      <c r="E133" s="25">
+      <c r="D133" s="41">
+        <v>78</v>
+      </c>
+      <c r="E133" s="24">
         <v>59</v>
       </c>
-      <c r="F133" s="40">
+      <c r="F133" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -4222,14 +4491,16 @@
       <c r="B134" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="C134" s="25">
+      <c r="C134" s="24">
         <v>92</v>
       </c>
-      <c r="D134" s="24"/>
-      <c r="E134" s="25">
+      <c r="D134" s="41">
+        <v>80</v>
+      </c>
+      <c r="E134" s="24">
         <v>59</v>
       </c>
-      <c r="F134" s="40">
+      <c r="F134" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4240,14 +4511,16 @@
       <c r="B135" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C135" s="25">
+      <c r="C135" s="24">
         <v>86</v>
       </c>
-      <c r="D135" s="24"/>
-      <c r="E135" s="25">
+      <c r="D135" s="41">
+        <v>89</v>
+      </c>
+      <c r="E135" s="24">
         <v>75</v>
       </c>
-      <c r="F135" s="40">
+      <c r="F135" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4258,14 +4531,16 @@
       <c r="B136" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C136" s="25">
+      <c r="C136" s="24">
         <v>85</v>
       </c>
-      <c r="D136" s="24"/>
-      <c r="E136" s="25">
+      <c r="D136" s="41">
+        <v>74</v>
+      </c>
+      <c r="E136" s="24">
         <v>50</v>
       </c>
-      <c r="F136" s="40">
+      <c r="F136" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4276,14 +4551,16 @@
       <c r="B137" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="C137" s="25">
+      <c r="C137" s="24">
         <v>95</v>
       </c>
-      <c r="D137" s="24"/>
-      <c r="E137" s="25">
+      <c r="D137" s="41">
+        <v>89</v>
+      </c>
+      <c r="E137" s="24">
         <v>59</v>
       </c>
-      <c r="F137" s="40">
+      <c r="F137" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4294,14 +4571,16 @@
       <c r="B138" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C138" s="25">
+      <c r="C138" s="24">
         <v>88</v>
       </c>
-      <c r="D138" s="24"/>
-      <c r="E138" s="25">
+      <c r="D138" s="41">
+        <v>86</v>
+      </c>
+      <c r="E138" s="24">
         <v>46</v>
       </c>
-      <c r="F138" s="40">
+      <c r="F138" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4312,14 +4591,16 @@
       <c r="B139" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C139" s="25">
+      <c r="C139" s="24">
         <v>93</v>
       </c>
-      <c r="D139" s="24"/>
-      <c r="E139" s="25">
-        <v>80</v>
-      </c>
-      <c r="F139" s="40">
+      <c r="D139" s="41">
+        <v>86</v>
+      </c>
+      <c r="E139" s="24">
+        <v>80</v>
+      </c>
+      <c r="F139" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4330,14 +4611,16 @@
       <c r="B140" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="C140" s="25">
+      <c r="C140" s="24">
         <v>75</v>
       </c>
-      <c r="D140" s="24"/>
-      <c r="E140" s="25">
-        <v>80</v>
-      </c>
-      <c r="F140" s="40">
+      <c r="D140" s="41">
+        <v>85</v>
+      </c>
+      <c r="E140" s="24">
+        <v>80</v>
+      </c>
+      <c r="F140" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4348,14 +4631,16 @@
       <c r="B141" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="C141" s="25">
+      <c r="C141" s="24">
         <v>88</v>
       </c>
-      <c r="D141" s="24"/>
-      <c r="E141" s="25">
+      <c r="D141" s="41">
+        <v>78</v>
+      </c>
+      <c r="E141" s="24">
         <v>40</v>
       </c>
-      <c r="F141" s="40">
+      <c r="F141" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -4366,14 +4651,16 @@
       <c r="B142" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="C142" s="25">
+      <c r="C142" s="24">
         <v>75</v>
       </c>
-      <c r="D142" s="24"/>
-      <c r="E142" s="25">
+      <c r="D142" s="41">
+        <v>85</v>
+      </c>
+      <c r="E142" s="24">
         <v>84</v>
       </c>
-      <c r="F142" s="40">
+      <c r="F142" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -4384,14 +4671,16 @@
       <c r="B143" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="C143" s="25">
-        <v>80</v>
-      </c>
-      <c r="D143" s="24"/>
-      <c r="E143" s="25">
+      <c r="C143" s="24">
+        <v>80</v>
+      </c>
+      <c r="D143" s="41">
+        <v>79</v>
+      </c>
+      <c r="E143" s="24">
         <v>82</v>
       </c>
-      <c r="F143" s="40">
+      <c r="F143" s="39">
         <v>85.71</v>
       </c>
     </row>
@@ -4402,14 +4691,16 @@
       <c r="B144" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C144" s="25">
+      <c r="C144" s="24">
         <v>89</v>
       </c>
-      <c r="D144" s="24"/>
-      <c r="E144" s="25">
+      <c r="D144" s="41">
+        <v>74</v>
+      </c>
+      <c r="E144" s="24">
         <v>66</v>
       </c>
-      <c r="F144" s="40">
+      <c r="F144" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4420,14 +4711,16 @@
       <c r="B145" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C145" s="25" t="s">
+      <c r="C145" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="D145" s="24"/>
-      <c r="E145" s="25">
+      <c r="D145" s="41">
+        <v>75</v>
+      </c>
+      <c r="E145" s="24">
         <v>51</v>
       </c>
-      <c r="F145" s="40">
+      <c r="F145" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -4438,14 +4731,16 @@
       <c r="B146" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="C146" s="25">
+      <c r="C146" s="24">
         <v>79</v>
       </c>
-      <c r="D146" s="24"/>
-      <c r="E146" s="25">
+      <c r="D146" s="41">
+        <v>75</v>
+      </c>
+      <c r="E146" s="24">
         <v>69</v>
       </c>
-      <c r="F146" s="40">
+      <c r="F146" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4456,14 +4751,16 @@
       <c r="B147" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C147" s="25">
+      <c r="C147" s="24">
         <v>85</v>
       </c>
-      <c r="D147" s="24"/>
-      <c r="E147" s="25">
+      <c r="D147" s="41">
+        <v>72</v>
+      </c>
+      <c r="E147" s="24">
         <v>75</v>
       </c>
-      <c r="F147" s="40">
+      <c r="F147" s="39">
         <v>90</v>
       </c>
     </row>
@@ -4474,14 +4771,16 @@
       <c r="B148" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C148" s="25">
+      <c r="C148" s="24">
         <v>90</v>
       </c>
-      <c r="D148" s="24"/>
-      <c r="E148" s="25">
+      <c r="D148" s="41">
+        <v>80</v>
+      </c>
+      <c r="E148" s="24">
         <v>58</v>
       </c>
-      <c r="F148" s="40">
+      <c r="F148" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4492,14 +4791,16 @@
       <c r="B149" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="C149" s="25">
-        <v>80</v>
-      </c>
-      <c r="D149" s="24"/>
-      <c r="E149" s="25">
+      <c r="C149" s="24">
+        <v>80</v>
+      </c>
+      <c r="D149" s="41">
+        <v>79</v>
+      </c>
+      <c r="E149" s="24">
         <v>75</v>
       </c>
-      <c r="F149" s="40">
+      <c r="F149" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4510,14 +4811,16 @@
       <c r="B150" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="C150" s="25">
-        <v>80</v>
-      </c>
-      <c r="D150" s="24"/>
-      <c r="E150" s="25">
+      <c r="C150" s="24">
+        <v>80</v>
+      </c>
+      <c r="D150" s="41">
+        <v>81</v>
+      </c>
+      <c r="E150" s="24">
         <v>62</v>
       </c>
-      <c r="F150" s="40">
+      <c r="F150" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4528,14 +4831,16 @@
       <c r="B151" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C151" s="25">
+      <c r="C151" s="24">
         <v>87</v>
       </c>
-      <c r="D151" s="24"/>
-      <c r="E151" s="25">
+      <c r="D151" s="41">
+        <v>72</v>
+      </c>
+      <c r="E151" s="24">
         <v>93</v>
       </c>
-      <c r="F151" s="40">
+      <c r="F151" s="39">
         <v>76.19</v>
       </c>
     </row>
@@ -4546,14 +4851,16 @@
       <c r="B152" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="C152" s="25">
+      <c r="C152" s="24">
         <v>85</v>
       </c>
-      <c r="D152" s="24"/>
-      <c r="E152" s="25">
+      <c r="D152" s="41">
+        <v>74</v>
+      </c>
+      <c r="E152" s="24">
         <v>71</v>
       </c>
-      <c r="F152" s="40">
+      <c r="F152" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4564,14 +4871,16 @@
       <c r="B153" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="C153" s="25">
+      <c r="C153" s="24">
         <v>81</v>
       </c>
-      <c r="D153" s="24"/>
-      <c r="E153" s="25">
+      <c r="D153" s="41">
+        <v>81</v>
+      </c>
+      <c r="E153" s="24">
         <v>91</v>
       </c>
-      <c r="F153" s="40">
+      <c r="F153" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4582,14 +4891,16 @@
       <c r="B154" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="C154" s="25">
+      <c r="C154" s="24">
         <v>88</v>
       </c>
-      <c r="D154" s="24"/>
-      <c r="E154" s="25">
+      <c r="D154" s="41">
+        <v>72</v>
+      </c>
+      <c r="E154" s="24">
         <v>88</v>
       </c>
-      <c r="F154" s="40">
+      <c r="F154" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4600,14 +4911,16 @@
       <c r="B155" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="C155" s="25">
+      <c r="C155" s="24">
         <v>88</v>
       </c>
-      <c r="D155" s="24"/>
-      <c r="E155" s="25">
+      <c r="D155" s="41">
+        <v>80</v>
+      </c>
+      <c r="E155" s="24">
         <v>65</v>
       </c>
-      <c r="F155" s="40">
+      <c r="F155" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4618,14 +4931,16 @@
       <c r="B156" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="C156" s="25">
+      <c r="C156" s="24">
         <v>85</v>
       </c>
-      <c r="D156" s="24"/>
-      <c r="E156" s="25">
+      <c r="D156" s="41">
+        <v>82</v>
+      </c>
+      <c r="E156" s="24">
         <v>83</v>
       </c>
-      <c r="F156" s="40">
+      <c r="F156" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4636,14 +4951,16 @@
       <c r="B157" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C157" s="25">
+      <c r="C157" s="24">
         <v>88</v>
       </c>
-      <c r="D157" s="24"/>
-      <c r="E157" s="25">
+      <c r="D157" s="41">
+        <v>79</v>
+      </c>
+      <c r="E157" s="24">
         <v>64</v>
       </c>
-      <c r="F157" s="40">
+      <c r="F157" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4654,14 +4971,16 @@
       <c r="B158" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C158" s="25">
+      <c r="C158" s="24">
         <v>81</v>
       </c>
-      <c r="D158" s="24"/>
-      <c r="E158" s="25">
+      <c r="D158" s="41">
+        <v>78</v>
+      </c>
+      <c r="E158" s="24">
         <v>68</v>
       </c>
-      <c r="F158" s="40">
+      <c r="F158" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4672,14 +4991,16 @@
       <c r="B159" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C159" s="25">
+      <c r="C159" s="24">
         <v>91</v>
       </c>
-      <c r="D159" s="24"/>
-      <c r="E159" s="25">
+      <c r="D159" s="41">
+        <v>74</v>
+      </c>
+      <c r="E159" s="24">
         <v>68</v>
       </c>
-      <c r="F159" s="40">
+      <c r="F159" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4690,14 +5011,16 @@
       <c r="B160" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C160" s="25">
+      <c r="C160" s="24">
         <v>86</v>
       </c>
-      <c r="D160" s="24"/>
-      <c r="E160" s="25">
+      <c r="D160" s="41">
+        <v>78</v>
+      </c>
+      <c r="E160" s="24">
         <v>85</v>
       </c>
-      <c r="F160" s="40">
+      <c r="F160" s="39">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4708,14 +5031,16 @@
       <c r="B161" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="C161" s="25">
-        <v>80</v>
-      </c>
-      <c r="D161" s="24"/>
-      <c r="E161" s="25">
+      <c r="C161" s="24">
+        <v>80</v>
+      </c>
+      <c r="D161" s="41">
+        <v>75</v>
+      </c>
+      <c r="E161" s="24">
         <v>54</v>
       </c>
-      <c r="F161" s="40">
+      <c r="F161" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4726,14 +5051,16 @@
       <c r="B162" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="C162" s="25">
+      <c r="C162" s="24">
         <v>94</v>
       </c>
-      <c r="D162" s="24"/>
-      <c r="E162" s="25">
+      <c r="D162" s="41">
+        <v>80</v>
+      </c>
+      <c r="E162" s="24">
         <v>54</v>
       </c>
-      <c r="F162" s="40">
+      <c r="F162" s="39">
         <v>90.48</v>
       </c>
     </row>
@@ -4744,14 +5071,16 @@
       <c r="B163" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="C163" s="25">
+      <c r="C163" s="24">
         <v>78</v>
       </c>
-      <c r="D163" s="24"/>
-      <c r="E163" s="25">
+      <c r="D163" s="41">
+        <v>72</v>
+      </c>
+      <c r="E163" s="24">
         <v>60</v>
       </c>
-      <c r="F163" s="40">
+      <c r="F163" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -4762,14 +5091,16 @@
       <c r="B164" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="C164" s="25">
+      <c r="C164" s="24">
         <v>87</v>
       </c>
-      <c r="D164" s="24"/>
-      <c r="E164" s="25">
+      <c r="D164" s="41">
+        <v>84</v>
+      </c>
+      <c r="E164" s="24">
         <v>59</v>
       </c>
-      <c r="F164" s="41">
+      <c r="F164" s="40">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -4780,14 +5111,16 @@
       <c r="B165" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="C165" s="25">
+      <c r="C165" s="24">
         <v>85</v>
       </c>
-      <c r="D165" s="24"/>
-      <c r="E165" s="25">
+      <c r="D165" s="41">
+        <v>78</v>
+      </c>
+      <c r="E165" s="24">
         <v>81</v>
       </c>
-      <c r="F165" s="41">
+      <c r="F165" s="40">
         <v>76.19</v>
       </c>
     </row>
@@ -4798,14 +5131,16 @@
       <c r="B166" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="C166" s="25">
-        <v>80</v>
-      </c>
-      <c r="D166" s="24"/>
-      <c r="E166" s="25">
+      <c r="C166" s="24">
+        <v>80</v>
+      </c>
+      <c r="D166" s="41">
+        <v>81</v>
+      </c>
+      <c r="E166" s="24">
         <v>87</v>
       </c>
-      <c r="F166" s="41">
+      <c r="F166" s="40">
         <v>80.95</v>
       </c>
     </row>
@@ -4816,14 +5151,16 @@
       <c r="B167" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="C167" s="25">
+      <c r="C167" s="24">
         <v>90</v>
       </c>
-      <c r="D167" s="24"/>
-      <c r="E167" s="25">
+      <c r="D167" s="41">
+        <v>81</v>
+      </c>
+      <c r="E167" s="24">
         <v>90</v>
       </c>
-      <c r="F167" s="41">
+      <c r="F167" s="40">
         <v>80.95</v>
       </c>
     </row>
@@ -4834,14 +5171,16 @@
       <c r="B168" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="C168" s="25">
-        <v>80</v>
-      </c>
-      <c r="D168" s="24"/>
-      <c r="E168" s="25">
+      <c r="C168" s="24">
+        <v>80</v>
+      </c>
+      <c r="D168" s="41">
+        <v>91</v>
+      </c>
+      <c r="E168" s="24">
         <v>59</v>
       </c>
-      <c r="F168" s="41">
+      <c r="F168" s="40">
         <v>90.48</v>
       </c>
     </row>
@@ -4852,14 +5191,16 @@
       <c r="B169" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C169" s="25">
-        <v>80</v>
-      </c>
-      <c r="D169" s="24"/>
-      <c r="E169" s="25">
+      <c r="C169" s="24">
+        <v>80</v>
+      </c>
+      <c r="D169" s="41">
+        <v>78</v>
+      </c>
+      <c r="E169" s="24">
         <v>59</v>
       </c>
-      <c r="F169" s="41">
+      <c r="F169" s="40">
         <v>66.67</v>
       </c>
     </row>
@@ -4870,14 +5211,16 @@
       <c r="B170" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="C170" s="25">
+      <c r="C170" s="24">
         <v>82</v>
       </c>
-      <c r="D170" s="24"/>
-      <c r="E170" s="25">
+      <c r="D170" s="41">
+        <v>89</v>
+      </c>
+      <c r="E170" s="24">
         <v>46</v>
       </c>
-      <c r="F170" s="41">
+      <c r="F170" s="40">
         <v>76.19</v>
       </c>
     </row>
@@ -4891,11 +5234,11 @@
       <c r="C171" s="22">
         <v>50</v>
       </c>
-      <c r="D171" s="24"/>
-      <c r="E171" s="25" t="s">
+      <c r="D171" s="41"/>
+      <c r="E171" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="F171" s="41">
+      <c r="F171" s="40">
         <v>14.29</v>
       </c>
     </row>
@@ -4909,11 +5252,13 @@
       <c r="C172" s="22">
         <v>50</v>
       </c>
-      <c r="D172" s="24"/>
-      <c r="E172" s="25">
+      <c r="D172" s="41">
+        <v>91</v>
+      </c>
+      <c r="E172" s="24">
         <v>55</v>
       </c>
-      <c r="F172" s="41">
+      <c r="F172" s="40">
         <v>76.19</v>
       </c>
     </row>
@@ -4924,14 +5269,16 @@
       <c r="B173" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="C173" s="25">
+      <c r="C173" s="24">
         <v>60</v>
       </c>
-      <c r="D173" s="24"/>
-      <c r="E173" s="25">
+      <c r="D173" s="41">
+        <v>91</v>
+      </c>
+      <c r="E173" s="24">
         <v>71</v>
       </c>
-      <c r="F173" s="41">
+      <c r="F173" s="40">
         <v>90.48</v>
       </c>
     </row>
@@ -4942,14 +5289,16 @@
       <c r="B174" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="C174" s="25">
+      <c r="C174" s="24">
         <v>75</v>
       </c>
-      <c r="D174" s="24"/>
-      <c r="E174" s="25">
+      <c r="D174" s="41">
+        <v>91</v>
+      </c>
+      <c r="E174" s="24">
         <v>67</v>
       </c>
-      <c r="F174" s="41">
+      <c r="F174" s="40">
         <v>80.95</v>
       </c>
     </row>
@@ -4960,14 +5309,16 @@
       <c r="B175" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="C175" s="25">
+      <c r="C175" s="24">
         <v>78</v>
       </c>
-      <c r="D175" s="24"/>
-      <c r="E175" s="25">
+      <c r="D175" s="41">
+        <v>91</v>
+      </c>
+      <c r="E175" s="24">
         <v>57</v>
       </c>
-      <c r="F175" s="41">
+      <c r="F175" s="40">
         <v>85.71</v>
       </c>
     </row>
@@ -4978,14 +5329,16 @@
       <c r="B176" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="C176" s="25">
+      <c r="C176" s="24">
         <v>79</v>
       </c>
-      <c r="D176" s="24"/>
-      <c r="E176" s="25">
+      <c r="D176" s="41">
+        <v>85</v>
+      </c>
+      <c r="E176" s="24">
         <v>54</v>
       </c>
-      <c r="F176" s="41">
+      <c r="F176" s="40">
         <v>66.67</v>
       </c>
     </row>
@@ -4996,14 +5349,14 @@
       <c r="B177" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="C177" s="25">
-        <v>80</v>
-      </c>
-      <c r="D177" s="24"/>
-      <c r="E177" s="25">
+      <c r="C177" s="24">
+        <v>80</v>
+      </c>
+      <c r="D177" s="41"/>
+      <c r="E177" s="24">
         <v>69</v>
       </c>
-      <c r="F177" s="41">
+      <c r="F177" s="40">
         <v>76.19</v>
       </c>
     </row>
@@ -5014,14 +5367,16 @@
       <c r="B178" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="C178" s="25">
+      <c r="C178" s="24">
         <v>50</v>
       </c>
-      <c r="D178" s="24"/>
-      <c r="E178" s="25">
+      <c r="D178" s="41">
+        <v>91</v>
+      </c>
+      <c r="E178" s="24">
         <v>56</v>
       </c>
-      <c r="F178" s="41">
+      <c r="F178" s="40">
         <v>90.48</v>
       </c>
     </row>
@@ -5032,14 +5387,16 @@
       <c r="B179" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="C179" s="25">
-        <v>80</v>
-      </c>
-      <c r="D179" s="24"/>
-      <c r="E179" s="25">
+      <c r="C179" s="24">
+        <v>80</v>
+      </c>
+      <c r="D179" s="41">
+        <v>91</v>
+      </c>
+      <c r="E179" s="24">
         <v>54</v>
       </c>
-      <c r="F179" s="41">
+      <c r="F179" s="40">
         <v>85.71</v>
       </c>
     </row>
@@ -5050,14 +5407,16 @@
       <c r="B180" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="C180" s="25">
-        <v>80</v>
-      </c>
-      <c r="D180" s="24"/>
-      <c r="E180" s="25">
+      <c r="C180" s="24">
+        <v>80</v>
+      </c>
+      <c r="D180" s="41">
+        <v>78</v>
+      </c>
+      <c r="E180" s="24">
         <v>57</v>
       </c>
-      <c r="F180" s="41">
+      <c r="F180" s="40">
         <v>76.19</v>
       </c>
     </row>
@@ -5068,14 +5427,16 @@
       <c r="B181" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="C181" s="25">
+      <c r="C181" s="24">
         <v>50</v>
       </c>
-      <c r="D181" s="24"/>
-      <c r="E181" s="25">
+      <c r="D181" s="41">
+        <v>91</v>
+      </c>
+      <c r="E181" s="24">
         <v>39</v>
       </c>
-      <c r="F181" s="41">
+      <c r="F181" s="40">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -5086,14 +5447,16 @@
       <c r="B182" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="C182" s="25">
+      <c r="C182" s="24">
         <v>85</v>
       </c>
-      <c r="D182" s="24"/>
-      <c r="E182" s="25">
+      <c r="D182" s="41">
+        <v>85</v>
+      </c>
+      <c r="E182" s="24">
         <v>52</v>
       </c>
-      <c r="F182" s="41">
+      <c r="F182" s="40">
         <v>76.19</v>
       </c>
     </row>
@@ -5104,14 +5467,14 @@
       <c r="B183" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="C183" s="25">
+      <c r="C183" s="24">
         <v>87</v>
       </c>
-      <c r="D183" s="24"/>
-      <c r="E183" s="25">
+      <c r="D183" s="41"/>
+      <c r="E183" s="24">
         <v>57</v>
       </c>
-      <c r="F183" s="40">
+      <c r="F183" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -5122,14 +5485,16 @@
       <c r="B184" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="C184" s="25">
+      <c r="C184" s="24">
         <v>85</v>
       </c>
-      <c r="D184" s="24"/>
-      <c r="E184" s="25">
+      <c r="D184" s="41">
+        <v>84</v>
+      </c>
+      <c r="E184" s="24">
         <v>69</v>
       </c>
-      <c r="F184" s="40">
+      <c r="F184" s="39">
         <v>80.95</v>
       </c>
     </row>
@@ -5140,422 +5505,426 @@
       <c r="B185" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="C185" s="25">
+      <c r="C185" s="24">
         <v>85</v>
       </c>
-      <c r="D185" s="24"/>
-      <c r="E185" s="25">
+      <c r="D185" s="41">
+        <v>80</v>
+      </c>
+      <c r="E185" s="24">
         <v>58</v>
       </c>
-      <c r="F185" s="40">
+      <c r="F185" s="39">
         <v>80.95</v>
       </c>
     </row>
     <row r="186" spans="1:6">
-      <c r="A186" s="27" t="s">
+      <c r="A186" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="B186" s="26" t="s">
+      <c r="B186" s="25" t="s">
         <v>373</v>
       </c>
-      <c r="C186" s="25" t="s">
+      <c r="C186" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="D186" s="24"/>
-      <c r="E186" s="25">
+      <c r="D186" s="41"/>
+      <c r="E186" s="24">
         <v>54</v>
       </c>
-      <c r="F186" s="40">
+      <c r="F186" s="39">
         <v>38.1</v>
       </c>
     </row>
     <row r="187" spans="1:6">
-      <c r="A187" s="27" t="s">
+      <c r="A187" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="B187" s="26" t="s">
+      <c r="B187" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="C187" s="25">
-        <v>80</v>
-      </c>
-      <c r="D187" s="24"/>
-      <c r="E187" s="25">
+      <c r="C187" s="24">
+        <v>80</v>
+      </c>
+      <c r="D187" s="41">
+        <v>80</v>
+      </c>
+      <c r="E187" s="24">
         <v>76</v>
       </c>
-      <c r="F187" s="40">
+      <c r="F187" s="39">
         <v>44.440000000000005</v>
       </c>
     </row>
     <row r="188" spans="1:6">
-      <c r="A188" s="27" t="s">
+      <c r="A188" s="26" t="s">
         <v>379</v>
       </c>
-      <c r="B188" s="26"/>
-      <c r="C188" s="25"/>
-      <c r="D188" s="24"/>
-      <c r="E188" s="25">
+      <c r="B188" s="25"/>
+      <c r="C188" s="24"/>
+      <c r="D188" s="41"/>
+      <c r="E188" s="24">
         <v>63</v>
       </c>
-      <c r="F188" s="40">
+      <c r="F188" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="27" t="s">
+      <c r="A189" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="B189" s="26"/>
-      <c r="C189" s="25"/>
-      <c r="D189" s="24"/>
-      <c r="E189" s="25">
+      <c r="B189" s="25"/>
+      <c r="C189" s="24"/>
+      <c r="D189" s="41"/>
+      <c r="E189" s="24">
         <v>26</v>
       </c>
-      <c r="F189" s="40">
+      <c r="F189" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:6">
-      <c r="A190" s="27" t="s">
+      <c r="A190" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="B190" s="26"/>
-      <c r="C190" s="25"/>
-      <c r="D190" s="24"/>
-      <c r="E190" s="25">
+      <c r="B190" s="25"/>
+      <c r="C190" s="24"/>
+      <c r="D190" s="41"/>
+      <c r="E190" s="24">
         <v>31</v>
       </c>
-      <c r="F190" s="40">
+      <c r="F190" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="A191" s="29"/>
-      <c r="B191" s="30"/>
+      <c r="A191" s="28"/>
+      <c r="B191" s="29"/>
       <c r="C191" s="4"/>
       <c r="D191" s="5"/>
       <c r="E191" s="4"/>
-      <c r="F191" s="34"/>
+      <c r="F191" s="33"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="A192" s="29"/>
-      <c r="B192" s="30"/>
+      <c r="A192" s="28"/>
+      <c r="B192" s="29"/>
       <c r="C192" s="4"/>
       <c r="D192" s="5"/>
       <c r="E192" s="4"/>
-      <c r="F192" s="34"/>
+      <c r="F192" s="33"/>
     </row>
     <row r="193" spans="1:6">
-      <c r="A193" s="31"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="29"/>
       <c r="C193" s="4"/>
       <c r="D193" s="5"/>
       <c r="E193" s="4"/>
-      <c r="F193" s="34"/>
+      <c r="F193" s="33"/>
     </row>
     <row r="194" spans="1:6">
-      <c r="A194" s="31"/>
-      <c r="B194" s="30"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="29"/>
       <c r="C194" s="4"/>
       <c r="D194" s="5"/>
       <c r="E194" s="4"/>
-      <c r="F194" s="34"/>
+      <c r="F194" s="33"/>
     </row>
     <row r="195" spans="1:6">
-      <c r="A195" s="29"/>
-      <c r="B195" s="30"/>
+      <c r="A195" s="28"/>
+      <c r="B195" s="29"/>
       <c r="C195" s="6"/>
       <c r="D195" s="5"/>
       <c r="E195" s="4"/>
-      <c r="F195" s="34"/>
+      <c r="F195" s="33"/>
     </row>
     <row r="196" spans="1:6">
-      <c r="A196" s="29"/>
-      <c r="B196" s="30"/>
+      <c r="A196" s="28"/>
+      <c r="B196" s="29"/>
       <c r="C196" s="6"/>
       <c r="D196" s="5"/>
       <c r="E196" s="4"/>
-      <c r="F196" s="34"/>
+      <c r="F196" s="33"/>
     </row>
     <row r="197" spans="1:6">
-      <c r="A197" s="29"/>
-      <c r="B197" s="30"/>
+      <c r="A197" s="28"/>
+      <c r="B197" s="29"/>
       <c r="C197" s="6"/>
       <c r="D197" s="5"/>
       <c r="E197" s="4"/>
-      <c r="F197" s="34"/>
+      <c r="F197" s="33"/>
     </row>
     <row r="198" spans="1:6">
-      <c r="A198" s="29"/>
-      <c r="B198" s="30"/>
+      <c r="A198" s="28"/>
+      <c r="B198" s="29"/>
       <c r="C198" s="6"/>
       <c r="D198" s="5"/>
       <c r="E198" s="4"/>
-      <c r="F198" s="34"/>
+      <c r="F198" s="33"/>
     </row>
     <row r="199" spans="1:6">
-      <c r="A199" s="29"/>
-      <c r="B199" s="30"/>
+      <c r="A199" s="28"/>
+      <c r="B199" s="29"/>
       <c r="C199" s="6"/>
       <c r="D199" s="5"/>
       <c r="E199" s="4"/>
-      <c r="F199" s="34"/>
+      <c r="F199" s="33"/>
     </row>
     <row r="200" spans="1:6">
-      <c r="A200" s="29"/>
-      <c r="B200" s="30"/>
+      <c r="A200" s="28"/>
+      <c r="B200" s="29"/>
       <c r="C200" s="6"/>
       <c r="D200" s="5"/>
       <c r="E200" s="4"/>
-      <c r="F200" s="34"/>
+      <c r="F200" s="33"/>
     </row>
     <row r="201" spans="1:6">
-      <c r="A201" s="32"/>
-      <c r="B201" s="33"/>
+      <c r="A201" s="31"/>
+      <c r="B201" s="32"/>
       <c r="C201" s="6"/>
       <c r="D201" s="5"/>
       <c r="E201" s="4"/>
-      <c r="F201" s="34"/>
+      <c r="F201" s="33"/>
     </row>
     <row r="202" spans="1:6">
-      <c r="A202" s="32"/>
-      <c r="B202" s="33"/>
+      <c r="A202" s="31"/>
+      <c r="B202" s="32"/>
       <c r="C202" s="6"/>
       <c r="D202" s="5"/>
       <c r="E202" s="4"/>
-      <c r="F202" s="34"/>
+      <c r="F202" s="33"/>
     </row>
     <row r="203" spans="1:6">
-      <c r="A203" s="32"/>
-      <c r="B203" s="33"/>
+      <c r="A203" s="31"/>
+      <c r="B203" s="32"/>
       <c r="C203" s="6"/>
       <c r="D203" s="5"/>
       <c r="E203" s="4"/>
-      <c r="F203" s="34"/>
+      <c r="F203" s="33"/>
     </row>
     <row r="204" spans="1:6">
-      <c r="A204" s="32"/>
-      <c r="B204" s="33"/>
+      <c r="A204" s="31"/>
+      <c r="B204" s="32"/>
       <c r="C204" s="6"/>
       <c r="D204" s="5"/>
       <c r="E204" s="4"/>
-      <c r="F204" s="34"/>
+      <c r="F204" s="33"/>
     </row>
     <row r="205" spans="1:6">
-      <c r="A205" s="32"/>
-      <c r="B205" s="33"/>
+      <c r="A205" s="31"/>
+      <c r="B205" s="32"/>
       <c r="C205" s="6"/>
       <c r="D205" s="5"/>
       <c r="E205" s="4"/>
-      <c r="F205" s="34"/>
+      <c r="F205" s="33"/>
     </row>
     <row r="206" spans="1:6">
-      <c r="A206" s="32"/>
-      <c r="B206" s="33"/>
+      <c r="A206" s="31"/>
+      <c r="B206" s="32"/>
       <c r="C206" s="6"/>
       <c r="D206" s="5"/>
       <c r="E206" s="4"/>
-      <c r="F206" s="34"/>
+      <c r="F206" s="33"/>
     </row>
     <row r="207" spans="1:6">
-      <c r="A207" s="32"/>
-      <c r="B207" s="33"/>
+      <c r="A207" s="31"/>
+      <c r="B207" s="32"/>
       <c r="C207" s="6"/>
       <c r="D207" s="5"/>
       <c r="E207" s="4"/>
-      <c r="F207" s="34"/>
+      <c r="F207" s="33"/>
     </row>
     <row r="208" spans="1:6">
-      <c r="A208" s="32"/>
-      <c r="B208" s="33"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="32"/>
       <c r="C208" s="6"/>
       <c r="D208" s="5"/>
       <c r="E208" s="4"/>
-      <c r="F208" s="34"/>
+      <c r="F208" s="33"/>
     </row>
     <row r="209" spans="1:6">
-      <c r="A209" s="32"/>
-      <c r="B209" s="33"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="32"/>
       <c r="C209" s="6"/>
       <c r="D209" s="5"/>
       <c r="E209" s="4"/>
-      <c r="F209" s="34"/>
+      <c r="F209" s="33"/>
     </row>
     <row r="210" spans="1:6">
-      <c r="A210" s="32"/>
-      <c r="B210" s="33"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="32"/>
       <c r="C210" s="6"/>
       <c r="D210" s="5"/>
       <c r="E210" s="4"/>
-      <c r="F210" s="34"/>
+      <c r="F210" s="33"/>
     </row>
     <row r="211" spans="1:6">
-      <c r="A211" s="32"/>
-      <c r="B211" s="33"/>
+      <c r="A211" s="31"/>
+      <c r="B211" s="32"/>
       <c r="C211" s="6"/>
       <c r="D211" s="5"/>
       <c r="E211" s="4"/>
-      <c r="F211" s="34"/>
+      <c r="F211" s="33"/>
     </row>
     <row r="212" spans="1:6">
-      <c r="A212" s="32"/>
-      <c r="B212" s="33"/>
+      <c r="A212" s="31"/>
+      <c r="B212" s="32"/>
       <c r="C212" s="6"/>
       <c r="D212" s="5"/>
       <c r="E212" s="4"/>
-      <c r="F212" s="34"/>
+      <c r="F212" s="33"/>
     </row>
     <row r="213" spans="1:6">
-      <c r="A213" s="32"/>
-      <c r="B213" s="33"/>
+      <c r="A213" s="31"/>
+      <c r="B213" s="32"/>
       <c r="C213" s="6"/>
       <c r="D213" s="5"/>
       <c r="E213" s="4"/>
-      <c r="F213" s="34"/>
+      <c r="F213" s="33"/>
     </row>
     <row r="214" spans="1:6">
-      <c r="A214" s="32"/>
-      <c r="B214" s="33"/>
+      <c r="A214" s="31"/>
+      <c r="B214" s="32"/>
       <c r="C214" s="6"/>
       <c r="D214" s="5"/>
       <c r="E214" s="4"/>
-      <c r="F214" s="34"/>
+      <c r="F214" s="33"/>
     </row>
     <row r="215" spans="1:6">
-      <c r="A215" s="32"/>
-      <c r="B215" s="33"/>
+      <c r="A215" s="31"/>
+      <c r="B215" s="32"/>
       <c r="C215" s="6"/>
       <c r="D215" s="5"/>
       <c r="E215" s="4"/>
-      <c r="F215" s="34"/>
+      <c r="F215" s="33"/>
     </row>
     <row r="216" spans="1:6">
-      <c r="A216" s="32"/>
-      <c r="B216" s="33"/>
+      <c r="A216" s="31"/>
+      <c r="B216" s="32"/>
       <c r="C216" s="6"/>
       <c r="D216" s="5"/>
       <c r="E216" s="4"/>
-      <c r="F216" s="34"/>
+      <c r="F216" s="33"/>
     </row>
     <row r="217" spans="1:6">
-      <c r="A217" s="32"/>
-      <c r="B217" s="33"/>
+      <c r="A217" s="31"/>
+      <c r="B217" s="32"/>
       <c r="C217" s="6"/>
       <c r="D217" s="5"/>
       <c r="E217" s="4"/>
-      <c r="F217" s="34"/>
+      <c r="F217" s="33"/>
     </row>
     <row r="218" spans="1:6">
-      <c r="A218" s="32"/>
-      <c r="B218" s="33"/>
+      <c r="A218" s="31"/>
+      <c r="B218" s="32"/>
       <c r="C218" s="6"/>
       <c r="D218" s="5"/>
       <c r="E218" s="4"/>
-      <c r="F218" s="34"/>
+      <c r="F218" s="33"/>
     </row>
     <row r="219" spans="1:6">
-      <c r="A219" s="32"/>
-      <c r="B219" s="33"/>
+      <c r="A219" s="31"/>
+      <c r="B219" s="32"/>
       <c r="C219" s="6"/>
       <c r="D219" s="5"/>
       <c r="E219" s="4"/>
-      <c r="F219" s="34"/>
+      <c r="F219" s="33"/>
     </row>
     <row r="220" spans="1:6">
-      <c r="A220" s="32"/>
-      <c r="B220" s="33"/>
+      <c r="A220" s="31"/>
+      <c r="B220" s="32"/>
       <c r="C220" s="6"/>
       <c r="D220" s="5"/>
       <c r="E220" s="4"/>
-      <c r="F220" s="34"/>
+      <c r="F220" s="33"/>
     </row>
     <row r="221" spans="1:6">
-      <c r="A221" s="32"/>
-      <c r="B221" s="33"/>
+      <c r="A221" s="31"/>
+      <c r="B221" s="32"/>
       <c r="C221" s="6"/>
       <c r="D221" s="5"/>
       <c r="E221" s="4"/>
-      <c r="F221" s="34"/>
+      <c r="F221" s="33"/>
     </row>
     <row r="222" spans="1:6">
-      <c r="A222" s="32"/>
-      <c r="B222" s="33"/>
+      <c r="A222" s="31"/>
+      <c r="B222" s="32"/>
       <c r="C222" s="6"/>
       <c r="D222" s="5"/>
       <c r="E222" s="4"/>
-      <c r="F222" s="34"/>
+      <c r="F222" s="33"/>
     </row>
     <row r="223" spans="1:6">
-      <c r="A223" s="32"/>
-      <c r="B223" s="33"/>
+      <c r="A223" s="31"/>
+      <c r="B223" s="32"/>
       <c r="C223" s="6"/>
       <c r="D223" s="5"/>
       <c r="E223" s="4"/>
-      <c r="F223" s="34"/>
+      <c r="F223" s="33"/>
     </row>
     <row r="224" spans="1:6">
-      <c r="A224" s="32"/>
-      <c r="B224" s="33"/>
+      <c r="A224" s="31"/>
+      <c r="B224" s="32"/>
       <c r="C224" s="6"/>
       <c r="D224" s="5"/>
       <c r="E224" s="4"/>
-      <c r="F224" s="34"/>
+      <c r="F224" s="33"/>
     </row>
     <row r="225" spans="1:6">
-      <c r="A225" s="32"/>
-      <c r="B225" s="33"/>
+      <c r="A225" s="31"/>
+      <c r="B225" s="32"/>
       <c r="C225" s="6"/>
       <c r="D225" s="5"/>
       <c r="E225" s="4"/>
-      <c r="F225" s="34"/>
+      <c r="F225" s="33"/>
     </row>
     <row r="226" spans="1:6">
-      <c r="A226" s="32"/>
-      <c r="B226" s="33"/>
+      <c r="A226" s="31"/>
+      <c r="B226" s="32"/>
       <c r="C226" s="6"/>
       <c r="D226" s="5"/>
       <c r="E226" s="4"/>
-      <c r="F226" s="34"/>
+      <c r="F226" s="33"/>
     </row>
     <row r="227" spans="1:6">
-      <c r="A227" s="35"/>
-      <c r="B227" s="36"/>
+      <c r="A227" s="34"/>
+      <c r="B227" s="35"/>
       <c r="C227" s="6"/>
       <c r="D227" s="5"/>
       <c r="E227" s="4"/>
-      <c r="F227" s="34"/>
+      <c r="F227" s="33"/>
     </row>
     <row r="228" spans="1:6">
-      <c r="A228" s="35"/>
-      <c r="B228" s="36"/>
+      <c r="A228" s="34"/>
+      <c r="B228" s="35"/>
       <c r="C228" s="6"/>
       <c r="D228" s="5"/>
       <c r="E228" s="4"/>
-      <c r="F228" s="34"/>
+      <c r="F228" s="33"/>
     </row>
     <row r="229" spans="1:6">
-      <c r="A229" s="35"/>
-      <c r="B229" s="36"/>
+      <c r="A229" s="34"/>
+      <c r="B229" s="35"/>
       <c r="C229" s="6"/>
       <c r="D229" s="5"/>
       <c r="E229" s="4"/>
-      <c r="F229" s="34"/>
+      <c r="F229" s="33"/>
     </row>
     <row r="230" spans="1:6">
-      <c r="A230" s="35"/>
-      <c r="B230" s="36"/>
+      <c r="A230" s="34"/>
+      <c r="B230" s="35"/>
       <c r="C230" s="6"/>
       <c r="D230" s="5"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="34"/>
+      <c r="F230" s="33"/>
     </row>
     <row r="231" spans="1:6">
-      <c r="A231" s="37"/>
-      <c r="B231" s="38"/>
+      <c r="A231" s="36"/>
+      <c r="B231" s="37"/>
       <c r="C231" s="6"/>
       <c r="D231" s="5"/>
       <c r="E231" s="4"/>
-      <c r="F231" s="34"/>
+      <c r="F231" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5708,18 +6077,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5729,6 +6098,12 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -5742,10 +6117,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
 </file>
--- a/ID7010_E22.xlsx
+++ b/ID7010_E22.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS-2024-2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7534444A-FC26-4D7A-BDE0-F97892B15E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1170,11 +1171,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1276,6 +1277,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1408,19 +1415,19 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1467,18 +1474,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1504,7 +1499,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1517,29 +1512,32 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="10" applyFont="1"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
-    <cellStyle name="60% - Accent1 2" xfId="1"/>
-    <cellStyle name="60% - Accent2 2" xfId="2"/>
-    <cellStyle name="60% - Accent3 2" xfId="3"/>
-    <cellStyle name="60% - Accent4 2" xfId="4"/>
-    <cellStyle name="60% - Accent5 2" xfId="5"/>
-    <cellStyle name="60% - Accent6 2" xfId="6"/>
+    <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Comma" xfId="10" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="13"/>
-    <cellStyle name="Neutral 2" xfId="7"/>
+    <cellStyle name="Comma 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Neutral 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="8"/>
-    <cellStyle name="Normal 3" xfId="11"/>
-    <cellStyle name="Normal 3 2" xfId="14"/>
-    <cellStyle name="Normal_Sheet1" xfId="12"/>
-    <cellStyle name="Title 2" xfId="9"/>
+    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal_Sheet1" xfId="12" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Title 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1811,17 +1809,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="39" style="27" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="27" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="38" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="27"/>
+    <col min="1" max="1" width="12.85546875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="39" style="23" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="34" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1">
@@ -1854,33 +1852,33 @@
       <c r="C2" s="4">
         <v>95</v>
       </c>
-      <c r="D2" s="41">
+      <c r="D2" s="37">
         <v>75</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="20">
         <v>56</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="35">
         <v>47.620000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="22" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="20">
         <v>78</v>
       </c>
-      <c r="D3" s="41">
+      <c r="D3" s="37">
         <v>84</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="20">
         <v>70</v>
       </c>
-      <c r="F3" s="39">
+      <c r="F3" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -1891,16 +1889,16 @@
       <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="20">
         <v>85</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="37">
         <v>84</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="20">
         <v>76</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="35">
         <v>23.810000000000002</v>
       </c>
     </row>
@@ -1911,16 +1909,16 @@
       <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="20">
         <v>97</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="37">
         <v>89</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="20">
         <v>90</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -1931,16 +1929,16 @@
       <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="20">
         <v>87</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="37">
         <v>89</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="20">
         <v>63</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -1951,16 +1949,16 @@
       <c r="B7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="20">
         <v>68</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="37">
         <v>84</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="20">
         <v>48</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="35">
         <v>61.9</v>
       </c>
     </row>
@@ -1971,16 +1969,16 @@
       <c r="B8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="24">
-        <v>80</v>
-      </c>
-      <c r="D8" s="41">
+      <c r="C8" s="20">
+        <v>80</v>
+      </c>
+      <c r="D8" s="37">
         <v>74</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="20">
         <v>83</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -1991,16 +1989,16 @@
       <c r="B9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="20">
         <v>98</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="37">
         <v>75</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="20">
         <v>82</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2011,16 +2009,16 @@
       <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="20">
         <v>89</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="37">
         <v>74</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="20">
         <v>73</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2031,16 +2029,16 @@
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="20">
         <v>96</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="37">
         <v>89</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="20">
         <v>82</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2051,16 +2049,16 @@
       <c r="B12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="20">
         <v>85</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="37">
         <v>82</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="20">
         <v>84</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2071,16 +2069,16 @@
       <c r="B13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="20">
         <v>85</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="37">
         <v>82</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="20">
         <v>81</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="35">
         <v>100</v>
       </c>
     </row>
@@ -2091,16 +2089,16 @@
       <c r="B14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="20">
         <v>96</v>
       </c>
-      <c r="D14" s="41">
-        <v>80</v>
-      </c>
-      <c r="E14" s="24">
+      <c r="D14" s="37">
+        <v>80</v>
+      </c>
+      <c r="E14" s="20">
         <v>66</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="35">
         <v>100</v>
       </c>
     </row>
@@ -2111,16 +2109,16 @@
       <c r="B15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="20">
         <v>85</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="37">
         <v>82</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="20">
         <v>87</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2131,16 +2129,16 @@
       <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="20">
         <v>82</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="37">
         <v>78</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="20">
         <v>79</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2151,16 +2149,16 @@
       <c r="B17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="20">
         <v>85</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="37">
         <v>72</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="20">
         <v>84</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2171,16 +2169,16 @@
       <c r="B18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="20">
         <v>88</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="37">
         <v>86</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="20">
         <v>83</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2191,16 +2189,16 @@
       <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="24">
-        <v>80</v>
-      </c>
-      <c r="D19" s="41">
+      <c r="C19" s="20">
+        <v>80</v>
+      </c>
+      <c r="D19" s="37">
         <v>81</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="20">
         <v>88</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2211,16 +2209,16 @@
       <c r="B20" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="20">
         <v>85</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="37">
         <v>81</v>
       </c>
-      <c r="E20" s="24">
-        <v>80</v>
-      </c>
-      <c r="F20" s="39">
+      <c r="E20" s="20">
+        <v>80</v>
+      </c>
+      <c r="F20" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -2231,16 +2229,16 @@
       <c r="B21" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="20">
         <v>94</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="37">
         <v>86</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="20">
         <v>74</v>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -2251,16 +2249,16 @@
       <c r="B22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="20">
         <v>89</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="37">
         <v>82</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="20">
         <v>91</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2271,16 +2269,16 @@
       <c r="B23" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="20">
         <v>73</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="37">
         <v>82</v>
       </c>
-      <c r="E23" s="24">
-        <v>80</v>
-      </c>
-      <c r="F23" s="39">
+      <c r="E23" s="20">
+        <v>80</v>
+      </c>
+      <c r="F23" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -2291,16 +2289,16 @@
       <c r="B24" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="24">
-        <v>80</v>
-      </c>
-      <c r="D24" s="41">
+      <c r="C24" s="20">
+        <v>80</v>
+      </c>
+      <c r="D24" s="37">
         <v>75</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="20">
         <v>85</v>
       </c>
-      <c r="F24" s="39">
+      <c r="F24" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2311,16 +2309,16 @@
       <c r="B25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="20">
         <v>78</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="37">
         <v>78</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="20">
         <v>84</v>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2331,16 +2329,16 @@
       <c r="B26" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="20">
         <v>85</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="37">
         <v>74</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="20">
         <v>82</v>
       </c>
-      <c r="F26" s="39">
+      <c r="F26" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2351,16 +2349,16 @@
       <c r="B27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="20">
         <v>94</v>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="37">
         <v>72</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="20">
         <v>83</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2371,16 +2369,16 @@
       <c r="B28" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="20">
         <v>91</v>
       </c>
-      <c r="D28" s="41">
+      <c r="D28" s="37">
         <v>72</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="20">
         <v>79</v>
       </c>
-      <c r="F28" s="39">
+      <c r="F28" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2391,16 +2389,16 @@
       <c r="B29" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="20">
         <v>88</v>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="37">
         <v>72</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="20">
         <v>79</v>
       </c>
-      <c r="F29" s="39">
+      <c r="F29" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2411,16 +2409,16 @@
       <c r="B30" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="20">
         <v>88</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="37">
         <v>75</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="20">
         <v>77</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2431,16 +2429,16 @@
       <c r="B31" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="20">
         <v>81</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="37">
         <v>78</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="20">
         <v>70</v>
       </c>
-      <c r="F31" s="39">
+      <c r="F31" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2451,16 +2449,16 @@
       <c r="B32" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="24">
-        <v>80</v>
-      </c>
-      <c r="D32" s="41">
+      <c r="C32" s="20">
+        <v>80</v>
+      </c>
+      <c r="D32" s="37">
         <v>79</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="20">
         <v>60</v>
       </c>
-      <c r="F32" s="39">
+      <c r="F32" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2471,16 +2469,16 @@
       <c r="B33" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="20">
         <v>81</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="37">
         <v>78</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="20">
         <v>84</v>
       </c>
-      <c r="F33" s="39">
+      <c r="F33" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2491,16 +2489,16 @@
       <c r="B34" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="24">
-        <v>80</v>
-      </c>
-      <c r="D34" s="41">
+      <c r="C34" s="20">
+        <v>80</v>
+      </c>
+      <c r="D34" s="37">
         <v>82</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="20">
         <v>49</v>
       </c>
-      <c r="F34" s="39">
+      <c r="F34" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2511,16 +2509,16 @@
       <c r="B35" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="24">
-        <v>80</v>
-      </c>
-      <c r="D35" s="41">
+      <c r="C35" s="20">
+        <v>80</v>
+      </c>
+      <c r="D35" s="37">
         <v>75</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="20">
         <v>67</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2531,16 +2529,16 @@
       <c r="B36" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="24">
-        <v>80</v>
-      </c>
-      <c r="D36" s="41">
+      <c r="C36" s="20">
+        <v>80</v>
+      </c>
+      <c r="D36" s="37">
         <v>72</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="20">
         <v>85</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2551,16 +2549,16 @@
       <c r="B37" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="20">
         <v>88</v>
       </c>
-      <c r="D37" s="41">
+      <c r="D37" s="37">
         <v>78</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="20">
         <v>79</v>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2571,16 +2569,16 @@
       <c r="B38" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="20">
         <v>73</v>
       </c>
-      <c r="D38" s="41">
+      <c r="D38" s="37">
         <v>82</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="20">
         <v>69</v>
       </c>
-      <c r="F38" s="39">
+      <c r="F38" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2591,16 +2589,16 @@
       <c r="B39" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="24">
-        <v>80</v>
-      </c>
-      <c r="D39" s="41">
+      <c r="C39" s="20">
+        <v>80</v>
+      </c>
+      <c r="D39" s="37">
         <v>79</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="20">
         <v>76</v>
       </c>
-      <c r="F39" s="39">
+      <c r="F39" s="35">
         <v>100</v>
       </c>
     </row>
@@ -2611,16 +2609,16 @@
       <c r="B40" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="20">
         <v>89</v>
       </c>
-      <c r="D40" s="41">
-        <v>80</v>
-      </c>
-      <c r="E40" s="24">
+      <c r="D40" s="37">
+        <v>80</v>
+      </c>
+      <c r="E40" s="20">
         <v>70</v>
       </c>
-      <c r="F40" s="39">
+      <c r="F40" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2631,16 +2629,16 @@
       <c r="B41" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="20">
         <v>96</v>
       </c>
-      <c r="D41" s="41">
+      <c r="D41" s="37">
         <v>86</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="20">
         <v>85</v>
       </c>
-      <c r="F41" s="39">
+      <c r="F41" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2651,16 +2649,16 @@
       <c r="B42" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="24">
+      <c r="C42" s="20">
         <v>78</v>
       </c>
-      <c r="D42" s="41">
+      <c r="D42" s="37">
         <v>82</v>
       </c>
-      <c r="E42" s="24">
+      <c r="E42" s="20">
         <v>75</v>
       </c>
-      <c r="F42" s="39">
+      <c r="F42" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2671,16 +2669,16 @@
       <c r="B43" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C43" s="24">
+      <c r="C43" s="20">
         <v>96</v>
       </c>
-      <c r="D43" s="41">
+      <c r="D43" s="37">
         <v>86</v>
       </c>
-      <c r="E43" s="24">
+      <c r="E43" s="20">
         <v>69</v>
       </c>
-      <c r="F43" s="39">
+      <c r="F43" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -2691,16 +2689,16 @@
       <c r="B44" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="24">
-        <v>80</v>
-      </c>
-      <c r="D44" s="41">
+      <c r="C44" s="20">
+        <v>80</v>
+      </c>
+      <c r="D44" s="37">
         <v>75</v>
       </c>
-      <c r="E44" s="24">
+      <c r="E44" s="20">
         <v>63</v>
       </c>
-      <c r="F44" s="39">
+      <c r="F44" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2711,16 +2709,16 @@
       <c r="B45" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="20">
         <v>91</v>
       </c>
-      <c r="D45" s="41">
+      <c r="D45" s="37">
         <v>72</v>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="20">
         <v>62</v>
       </c>
-      <c r="F45" s="39">
+      <c r="F45" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2731,16 +2729,16 @@
       <c r="B46" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="20">
         <v>84</v>
       </c>
-      <c r="D46" s="41">
+      <c r="D46" s="37">
         <v>86</v>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="20">
         <v>81</v>
       </c>
-      <c r="F46" s="39">
+      <c r="F46" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -2751,16 +2749,16 @@
       <c r="B47" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="20">
         <v>85</v>
       </c>
-      <c r="D47" s="41">
+      <c r="D47" s="37">
         <v>72</v>
       </c>
-      <c r="E47" s="24">
-        <v>80</v>
-      </c>
-      <c r="F47" s="39">
+      <c r="E47" s="20">
+        <v>80</v>
+      </c>
+      <c r="F47" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2771,16 +2769,16 @@
       <c r="B48" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="24">
-        <v>80</v>
-      </c>
-      <c r="D48" s="41">
+      <c r="C48" s="20">
+        <v>80</v>
+      </c>
+      <c r="D48" s="37">
         <v>75</v>
       </c>
-      <c r="E48" s="24">
+      <c r="E48" s="20">
         <v>77</v>
       </c>
-      <c r="F48" s="39">
+      <c r="F48" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2791,16 +2789,16 @@
       <c r="B49" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="24">
+      <c r="C49" s="20">
         <v>85</v>
       </c>
-      <c r="D49" s="41">
+      <c r="D49" s="37">
         <v>78</v>
       </c>
-      <c r="E49" s="24">
+      <c r="E49" s="20">
         <v>88</v>
       </c>
-      <c r="F49" s="39">
+      <c r="F49" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2811,16 +2809,16 @@
       <c r="B50" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="24">
+      <c r="C50" s="20">
         <v>68</v>
       </c>
-      <c r="D50" s="41">
+      <c r="D50" s="37">
         <v>82</v>
       </c>
-      <c r="E50" s="24">
+      <c r="E50" s="20">
         <v>85</v>
       </c>
-      <c r="F50" s="39">
+      <c r="F50" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2831,16 +2829,16 @@
       <c r="B51" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="24">
-        <v>80</v>
-      </c>
-      <c r="D51" s="41">
+      <c r="C51" s="20">
+        <v>80</v>
+      </c>
+      <c r="D51" s="37">
         <v>72</v>
       </c>
-      <c r="E51" s="24">
+      <c r="E51" s="20">
         <v>48</v>
       </c>
-      <c r="F51" s="39">
+      <c r="F51" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2851,16 +2849,16 @@
       <c r="B52" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="24">
-        <v>80</v>
-      </c>
-      <c r="D52" s="41">
+      <c r="C52" s="20">
+        <v>80</v>
+      </c>
+      <c r="D52" s="37">
         <v>79</v>
       </c>
-      <c r="E52" s="24">
+      <c r="E52" s="20">
         <v>78</v>
       </c>
-      <c r="F52" s="39">
+      <c r="F52" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2871,16 +2869,16 @@
       <c r="B53" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="24">
+      <c r="C53" s="20">
         <v>90</v>
       </c>
-      <c r="D53" s="41">
+      <c r="D53" s="37">
         <v>72</v>
       </c>
-      <c r="E53" s="24">
-        <v>80</v>
-      </c>
-      <c r="F53" s="39">
+      <c r="E53" s="20">
+        <v>80</v>
+      </c>
+      <c r="F53" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -2891,16 +2889,16 @@
       <c r="B54" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C54" s="24">
+      <c r="C54" s="20">
         <v>85</v>
       </c>
-      <c r="D54" s="41">
+      <c r="D54" s="37">
         <v>74</v>
       </c>
-      <c r="E54" s="24">
+      <c r="E54" s="20">
         <v>56</v>
       </c>
-      <c r="F54" s="39">
+      <c r="F54" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2911,16 +2909,16 @@
       <c r="B55" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C55" s="20">
         <v>85</v>
       </c>
-      <c r="D55" s="41">
+      <c r="D55" s="37">
         <v>62</v>
       </c>
-      <c r="E55" s="24">
+      <c r="E55" s="20">
         <v>81</v>
       </c>
-      <c r="F55" s="39">
+      <c r="F55" s="35">
         <v>66.67</v>
       </c>
     </row>
@@ -2931,16 +2929,16 @@
       <c r="B56" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="24">
-        <v>80</v>
-      </c>
-      <c r="D56" s="41">
+      <c r="C56" s="20">
+        <v>80</v>
+      </c>
+      <c r="D56" s="37">
         <v>62</v>
       </c>
-      <c r="E56" s="24">
+      <c r="E56" s="20">
         <v>75</v>
       </c>
-      <c r="F56" s="39">
+      <c r="F56" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2951,16 +2949,16 @@
       <c r="B57" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="24">
+      <c r="C57" s="20">
         <v>85</v>
       </c>
-      <c r="D57" s="41">
+      <c r="D57" s="37">
         <v>75</v>
       </c>
-      <c r="E57" s="24">
+      <c r="E57" s="20">
         <v>82</v>
       </c>
-      <c r="F57" s="39">
+      <c r="F57" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2971,16 +2969,16 @@
       <c r="B58" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="24">
-        <v>80</v>
-      </c>
-      <c r="D58" s="41">
+      <c r="C58" s="20">
+        <v>80</v>
+      </c>
+      <c r="D58" s="37">
         <v>72</v>
       </c>
-      <c r="E58" s="24">
+      <c r="E58" s="20">
         <v>70</v>
       </c>
-      <c r="F58" s="39">
+      <c r="F58" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -2991,36 +2989,36 @@
       <c r="B59" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C59" s="24">
+      <c r="C59" s="20">
         <v>86</v>
       </c>
-      <c r="D59" s="41">
+      <c r="D59" s="37">
         <v>89</v>
       </c>
-      <c r="E59" s="24">
-        <v>80</v>
-      </c>
-      <c r="F59" s="39">
+      <c r="E59" s="20">
+        <v>80</v>
+      </c>
+      <c r="F59" s="35">
         <v>85.71</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="26" t="s">
+      <c r="A60" s="22" t="s">
         <v>122</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="24">
+      <c r="C60" s="20">
         <v>85</v>
       </c>
-      <c r="D60" s="41">
+      <c r="D60" s="37">
         <v>81</v>
       </c>
-      <c r="E60" s="24">
+      <c r="E60" s="20">
         <v>81</v>
       </c>
-      <c r="F60" s="39">
+      <c r="F60" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3031,16 +3029,16 @@
       <c r="B61" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C61" s="24">
+      <c r="C61" s="20">
         <v>86</v>
       </c>
-      <c r="D61" s="41">
+      <c r="D61" s="37">
         <v>89</v>
       </c>
-      <c r="E61" s="24">
+      <c r="E61" s="20">
         <v>71</v>
       </c>
-      <c r="F61" s="39">
+      <c r="F61" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3051,16 +3049,16 @@
       <c r="B62" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C62" s="24">
+      <c r="C62" s="20">
         <v>92</v>
       </c>
-      <c r="D62" s="41">
+      <c r="D62" s="37">
         <v>75</v>
       </c>
-      <c r="E62" s="24">
+      <c r="E62" s="20">
         <v>81</v>
       </c>
-      <c r="F62" s="39">
+      <c r="F62" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3071,16 +3069,16 @@
       <c r="B63" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C63" s="24">
+      <c r="C63" s="20">
         <v>85</v>
       </c>
-      <c r="D63" s="41">
+      <c r="D63" s="37">
         <v>84</v>
       </c>
-      <c r="E63" s="24">
+      <c r="E63" s="20">
         <v>74</v>
       </c>
-      <c r="F63" s="39">
+      <c r="F63" s="35">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -3091,16 +3089,16 @@
       <c r="B64" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C64" s="24">
-        <v>80</v>
-      </c>
-      <c r="D64" s="41">
+      <c r="C64" s="20">
+        <v>80</v>
+      </c>
+      <c r="D64" s="37">
         <v>75</v>
       </c>
-      <c r="E64" s="24">
+      <c r="E64" s="20">
         <v>78</v>
       </c>
-      <c r="F64" s="39">
+      <c r="F64" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3111,16 +3109,16 @@
       <c r="B65" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C65" s="24">
+      <c r="C65" s="20">
         <v>75</v>
       </c>
-      <c r="D65" s="41">
+      <c r="D65" s="37">
         <v>85</v>
       </c>
-      <c r="E65" s="24">
+      <c r="E65" s="20">
         <v>51</v>
       </c>
-      <c r="F65" s="39">
+      <c r="F65" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3131,16 +3129,16 @@
       <c r="B66" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C66" s="24">
+      <c r="C66" s="20">
         <v>90</v>
       </c>
-      <c r="D66" s="41">
+      <c r="D66" s="37">
         <v>89</v>
       </c>
-      <c r="E66" s="24">
+      <c r="E66" s="20">
         <v>50</v>
       </c>
-      <c r="F66" s="39">
+      <c r="F66" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -3151,16 +3149,16 @@
       <c r="B67" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C67" s="24">
+      <c r="C67" s="20">
         <v>93</v>
       </c>
-      <c r="D67" s="41">
+      <c r="D67" s="37">
         <v>79</v>
       </c>
-      <c r="E67" s="24">
+      <c r="E67" s="20">
         <v>78</v>
       </c>
-      <c r="F67" s="39">
+      <c r="F67" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3171,16 +3169,16 @@
       <c r="B68" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C68" s="24">
+      <c r="C68" s="20">
         <v>86</v>
       </c>
-      <c r="D68" s="41">
+      <c r="D68" s="37">
         <v>89</v>
       </c>
-      <c r="E68" s="24">
+      <c r="E68" s="20">
         <v>73</v>
       </c>
-      <c r="F68" s="39">
+      <c r="F68" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -3191,16 +3189,16 @@
       <c r="B69" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C69" s="24">
+      <c r="C69" s="20">
         <v>93</v>
       </c>
-      <c r="D69" s="41">
+      <c r="D69" s="37">
         <v>62</v>
       </c>
-      <c r="E69" s="24">
+      <c r="E69" s="20">
         <v>63</v>
       </c>
-      <c r="F69" s="39">
+      <c r="F69" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -3211,16 +3209,16 @@
       <c r="B70" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C70" s="24">
-        <v>80</v>
-      </c>
-      <c r="D70" s="41">
+      <c r="C70" s="20">
+        <v>80</v>
+      </c>
+      <c r="D70" s="37">
         <v>79</v>
       </c>
-      <c r="E70" s="24">
+      <c r="E70" s="20">
         <v>83</v>
       </c>
-      <c r="F70" s="39">
+      <c r="F70" s="35">
         <v>100</v>
       </c>
     </row>
@@ -3231,16 +3229,16 @@
       <c r="B71" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C71" s="24">
+      <c r="C71" s="20">
         <v>97</v>
       </c>
-      <c r="D71" s="41">
+      <c r="D71" s="37">
         <v>86</v>
       </c>
-      <c r="E71" s="24">
+      <c r="E71" s="20">
         <v>83</v>
       </c>
-      <c r="F71" s="39">
+      <c r="F71" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3251,16 +3249,16 @@
       <c r="B72" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C72" s="24">
-        <v>80</v>
-      </c>
-      <c r="D72" s="41">
+      <c r="C72" s="20">
+        <v>80</v>
+      </c>
+      <c r="D72" s="37">
         <v>81</v>
       </c>
-      <c r="E72" s="24">
+      <c r="E72" s="20">
         <v>65</v>
       </c>
-      <c r="F72" s="39">
+      <c r="F72" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3271,16 +3269,16 @@
       <c r="B73" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C73" s="24">
+      <c r="C73" s="20">
         <v>86</v>
       </c>
-      <c r="D73" s="41">
+      <c r="D73" s="37">
         <v>78</v>
       </c>
-      <c r="E73" s="24">
+      <c r="E73" s="20">
         <v>87</v>
       </c>
-      <c r="F73" s="39">
+      <c r="F73" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3291,16 +3289,16 @@
       <c r="B74" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="C74" s="24">
+      <c r="C74" s="20">
         <v>85</v>
       </c>
-      <c r="D74" s="41">
-        <v>80</v>
-      </c>
-      <c r="E74" s="24">
+      <c r="D74" s="37">
+        <v>80</v>
+      </c>
+      <c r="E74" s="20">
         <v>85</v>
       </c>
-      <c r="F74" s="39">
+      <c r="F74" s="35">
         <v>100</v>
       </c>
     </row>
@@ -3311,16 +3309,16 @@
       <c r="B75" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C75" s="24">
+      <c r="C75" s="20">
         <v>93</v>
       </c>
-      <c r="D75" s="41">
+      <c r="D75" s="37">
         <v>82</v>
       </c>
-      <c r="E75" s="24">
+      <c r="E75" s="20">
         <v>90</v>
       </c>
-      <c r="F75" s="39">
+      <c r="F75" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3331,16 +3329,16 @@
       <c r="B76" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C76" s="24">
+      <c r="C76" s="20">
         <v>85</v>
       </c>
-      <c r="D76" s="41">
-        <v>80</v>
-      </c>
-      <c r="E76" s="24">
+      <c r="D76" s="37">
+        <v>80</v>
+      </c>
+      <c r="E76" s="20">
         <v>87</v>
       </c>
-      <c r="F76" s="39">
+      <c r="F76" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3351,16 +3349,16 @@
       <c r="B77" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C77" s="24">
+      <c r="C77" s="20">
         <v>95</v>
       </c>
-      <c r="D77" s="41">
+      <c r="D77" s="37">
         <v>89</v>
       </c>
-      <c r="E77" s="24">
-        <v>80</v>
-      </c>
-      <c r="F77" s="39">
+      <c r="E77" s="20">
+        <v>80</v>
+      </c>
+      <c r="F77" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3371,16 +3369,16 @@
       <c r="B78" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C78" s="24">
+      <c r="C78" s="20">
         <v>90</v>
       </c>
-      <c r="D78" s="41">
-        <v>80</v>
-      </c>
-      <c r="E78" s="24">
+      <c r="D78" s="37">
+        <v>80</v>
+      </c>
+      <c r="E78" s="20">
         <v>76</v>
       </c>
-      <c r="F78" s="39">
+      <c r="F78" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -3391,16 +3389,16 @@
       <c r="B79" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C79" s="24">
-        <v>80</v>
-      </c>
-      <c r="D79" s="41">
+      <c r="C79" s="20">
+        <v>80</v>
+      </c>
+      <c r="D79" s="37">
         <v>72</v>
       </c>
-      <c r="E79" s="24">
+      <c r="E79" s="20">
         <v>85</v>
       </c>
-      <c r="F79" s="39">
+      <c r="F79" s="35">
         <v>100</v>
       </c>
     </row>
@@ -3411,16 +3409,16 @@
       <c r="B80" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C80" s="24">
+      <c r="C80" s="20">
         <v>95</v>
       </c>
-      <c r="D80" s="41">
+      <c r="D80" s="37">
         <v>79</v>
       </c>
-      <c r="E80" s="24">
+      <c r="E80" s="20">
         <v>87</v>
       </c>
-      <c r="F80" s="39">
+      <c r="F80" s="35">
         <v>100</v>
       </c>
     </row>
@@ -3431,16 +3429,16 @@
       <c r="B81" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C81" s="24">
+      <c r="C81" s="20">
         <v>89</v>
       </c>
-      <c r="D81" s="41">
+      <c r="D81" s="37">
         <v>78</v>
       </c>
-      <c r="E81" s="24">
+      <c r="E81" s="20">
         <v>84</v>
       </c>
-      <c r="F81" s="39">
+      <c r="F81" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3451,16 +3449,16 @@
       <c r="B82" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C82" s="24">
+      <c r="C82" s="20">
         <v>87</v>
       </c>
-      <c r="D82" s="41">
+      <c r="D82" s="37">
         <v>84</v>
       </c>
-      <c r="E82" s="24">
+      <c r="E82" s="20">
         <v>60</v>
       </c>
-      <c r="F82" s="39">
+      <c r="F82" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -3471,16 +3469,16 @@
       <c r="B83" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C83" s="24">
+      <c r="C83" s="20">
         <v>87</v>
       </c>
-      <c r="D83" s="41">
+      <c r="D83" s="37">
         <v>82</v>
       </c>
-      <c r="E83" s="24">
+      <c r="E83" s="20">
         <v>69</v>
       </c>
-      <c r="F83" s="39">
+      <c r="F83" s="35">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -3491,16 +3489,16 @@
       <c r="B84" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C84" s="24">
-        <v>80</v>
-      </c>
-      <c r="D84" s="41">
+      <c r="C84" s="20">
+        <v>80</v>
+      </c>
+      <c r="D84" s="37">
         <v>84</v>
       </c>
-      <c r="E84" s="24">
+      <c r="E84" s="20">
         <v>85</v>
       </c>
-      <c r="F84" s="39">
+      <c r="F84" s="35">
         <v>66.67</v>
       </c>
     </row>
@@ -3511,16 +3509,16 @@
       <c r="B85" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C85" s="24">
+      <c r="C85" s="20">
         <v>85</v>
       </c>
-      <c r="D85" s="41">
+      <c r="D85" s="37">
         <v>84</v>
       </c>
-      <c r="E85" s="24">
+      <c r="E85" s="20">
         <v>78</v>
       </c>
-      <c r="F85" s="39">
+      <c r="F85" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -3531,16 +3529,16 @@
       <c r="B86" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C86" s="24">
+      <c r="C86" s="20">
         <v>88</v>
       </c>
-      <c r="D86" s="41">
+      <c r="D86" s="37">
         <v>82</v>
       </c>
-      <c r="E86" s="24">
+      <c r="E86" s="20">
         <v>83</v>
       </c>
-      <c r="F86" s="39">
+      <c r="F86" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3551,16 +3549,16 @@
       <c r="B87" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C87" s="24">
+      <c r="C87" s="20">
         <v>91</v>
       </c>
-      <c r="D87" s="41">
+      <c r="D87" s="37">
         <v>84</v>
       </c>
-      <c r="E87" s="24">
+      <c r="E87" s="20">
         <v>51</v>
       </c>
-      <c r="F87" s="39">
+      <c r="F87" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3571,16 +3569,16 @@
       <c r="B88" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C88" s="24">
+      <c r="C88" s="20">
         <v>87</v>
       </c>
-      <c r="D88" s="41">
+      <c r="D88" s="37">
         <v>89</v>
       </c>
-      <c r="E88" s="24">
+      <c r="E88" s="20">
         <v>68</v>
       </c>
-      <c r="F88" s="39">
+      <c r="F88" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3591,16 +3589,16 @@
       <c r="B89" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C89" s="24">
+      <c r="C89" s="20">
         <v>85</v>
       </c>
-      <c r="D89" s="41">
+      <c r="D89" s="37">
         <v>78</v>
       </c>
-      <c r="E89" s="24">
+      <c r="E89" s="20">
         <v>83</v>
       </c>
-      <c r="F89" s="39">
+      <c r="F89" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -3611,16 +3609,16 @@
       <c r="B90" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C90" s="24">
+      <c r="C90" s="20">
         <v>75</v>
       </c>
-      <c r="D90" s="41">
+      <c r="D90" s="37">
         <v>85</v>
       </c>
-      <c r="E90" s="24">
+      <c r="E90" s="20">
         <v>81</v>
       </c>
-      <c r="F90" s="39">
+      <c r="F90" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3631,16 +3629,16 @@
       <c r="B91" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C91" s="24">
+      <c r="C91" s="20">
         <v>83</v>
       </c>
-      <c r="D91" s="41">
+      <c r="D91" s="37">
         <v>85</v>
       </c>
-      <c r="E91" s="24">
+      <c r="E91" s="20">
         <v>84</v>
       </c>
-      <c r="F91" s="39">
+      <c r="F91" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3651,16 +3649,16 @@
       <c r="B92" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C92" s="24">
+      <c r="C92" s="20">
         <v>96</v>
       </c>
-      <c r="D92" s="41">
-        <v>80</v>
-      </c>
-      <c r="E92" s="24">
+      <c r="D92" s="37">
+        <v>80</v>
+      </c>
+      <c r="E92" s="20">
         <v>85</v>
       </c>
-      <c r="F92" s="39">
+      <c r="F92" s="35">
         <v>100</v>
       </c>
     </row>
@@ -3671,16 +3669,16 @@
       <c r="B93" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C93" s="24">
+      <c r="C93" s="20">
         <v>70</v>
       </c>
-      <c r="D93" s="41">
+      <c r="D93" s="37">
         <v>82</v>
       </c>
-      <c r="E93" s="24">
+      <c r="E93" s="20">
         <v>78</v>
       </c>
-      <c r="F93" s="39">
+      <c r="F93" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -3691,16 +3689,16 @@
       <c r="B94" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C94" s="24">
+      <c r="C94" s="20">
         <v>85</v>
       </c>
-      <c r="D94" s="41">
+      <c r="D94" s="37">
         <v>78</v>
       </c>
-      <c r="E94" s="24">
+      <c r="E94" s="20">
         <v>67</v>
       </c>
-      <c r="F94" s="39">
+      <c r="F94" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3711,16 +3709,16 @@
       <c r="B95" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C95" s="24">
-        <v>80</v>
-      </c>
-      <c r="D95" s="41">
+      <c r="C95" s="20">
+        <v>80</v>
+      </c>
+      <c r="D95" s="37">
         <v>62</v>
       </c>
-      <c r="E95" s="24">
+      <c r="E95" s="20">
         <v>75</v>
       </c>
-      <c r="F95" s="39">
+      <c r="F95" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3731,16 +3729,16 @@
       <c r="B96" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C96" s="24">
+      <c r="C96" s="20">
         <v>89</v>
       </c>
-      <c r="D96" s="41">
+      <c r="D96" s="37">
         <v>85</v>
       </c>
-      <c r="E96" s="24">
+      <c r="E96" s="20">
         <v>81</v>
       </c>
-      <c r="F96" s="39">
+      <c r="F96" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3751,16 +3749,16 @@
       <c r="B97" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C97" s="24">
+      <c r="C97" s="20">
         <v>85</v>
       </c>
-      <c r="D97" s="41">
+      <c r="D97" s="37">
         <v>72</v>
       </c>
-      <c r="E97" s="24">
+      <c r="E97" s="20">
         <v>67</v>
       </c>
-      <c r="F97" s="39">
+      <c r="F97" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -3771,16 +3769,16 @@
       <c r="B98" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C98" s="24">
+      <c r="C98" s="20">
         <v>85</v>
       </c>
-      <c r="D98" s="41">
+      <c r="D98" s="37">
         <v>81</v>
       </c>
-      <c r="E98" s="24">
+      <c r="E98" s="20">
         <v>82</v>
       </c>
-      <c r="F98" s="39">
+      <c r="F98" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3791,16 +3789,16 @@
       <c r="B99" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C99" s="24">
+      <c r="C99" s="20">
         <v>88</v>
       </c>
-      <c r="D99" s="41">
-        <v>80</v>
-      </c>
-      <c r="E99" s="24">
+      <c r="D99" s="37">
+        <v>80</v>
+      </c>
+      <c r="E99" s="20">
         <v>87</v>
       </c>
-      <c r="F99" s="39">
+      <c r="F99" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3811,16 +3809,16 @@
       <c r="B100" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="C100" s="24">
+      <c r="C100" s="20">
         <v>87</v>
       </c>
-      <c r="D100" s="41">
-        <v>80</v>
-      </c>
-      <c r="E100" s="24">
+      <c r="D100" s="37">
+        <v>80</v>
+      </c>
+      <c r="E100" s="20">
         <v>87</v>
       </c>
-      <c r="F100" s="39">
+      <c r="F100" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3831,16 +3829,16 @@
       <c r="B101" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C101" s="24">
+      <c r="C101" s="20">
         <v>88</v>
       </c>
-      <c r="D101" s="41">
+      <c r="D101" s="37">
         <v>82</v>
       </c>
-      <c r="E101" s="24">
+      <c r="E101" s="20">
         <v>65</v>
       </c>
-      <c r="F101" s="39">
+      <c r="F101" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3851,16 +3849,16 @@
       <c r="B102" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C102" s="24">
+      <c r="C102" s="20">
         <v>94</v>
       </c>
-      <c r="D102" s="41">
+      <c r="D102" s="37">
         <v>79</v>
       </c>
-      <c r="E102" s="24">
+      <c r="E102" s="20">
         <v>72</v>
       </c>
-      <c r="F102" s="39">
+      <c r="F102" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3871,16 +3869,16 @@
       <c r="B103" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C103" s="24">
+      <c r="C103" s="20">
         <v>89</v>
       </c>
-      <c r="D103" s="41">
+      <c r="D103" s="37">
         <v>72</v>
       </c>
-      <c r="E103" s="24">
+      <c r="E103" s="20">
         <v>40</v>
       </c>
-      <c r="F103" s="39">
+      <c r="F103" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -3891,16 +3889,16 @@
       <c r="B104" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C104" s="24">
+      <c r="C104" s="20">
         <v>88</v>
       </c>
-      <c r="D104" s="41">
-        <v>80</v>
-      </c>
-      <c r="E104" s="24">
+      <c r="D104" s="37">
+        <v>80</v>
+      </c>
+      <c r="E104" s="20">
         <v>55</v>
       </c>
-      <c r="F104" s="39">
+      <c r="F104" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -3911,16 +3909,16 @@
       <c r="B105" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C105" s="24">
+      <c r="C105" s="20">
         <v>91</v>
       </c>
-      <c r="D105" s="41">
+      <c r="D105" s="37">
         <v>82</v>
       </c>
-      <c r="E105" s="24">
+      <c r="E105" s="20">
         <v>79</v>
       </c>
-      <c r="F105" s="39">
+      <c r="F105" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3931,16 +3929,16 @@
       <c r="B106" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C106" s="24">
+      <c r="C106" s="20">
         <v>90</v>
       </c>
-      <c r="D106" s="41">
-        <v>80</v>
-      </c>
-      <c r="E106" s="24">
+      <c r="D106" s="37">
+        <v>80</v>
+      </c>
+      <c r="E106" s="20">
         <v>44</v>
       </c>
-      <c r="F106" s="39">
+      <c r="F106" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -3951,16 +3949,16 @@
       <c r="B107" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C107" s="24">
-        <v>80</v>
-      </c>
-      <c r="D107" s="41">
+      <c r="C107" s="20">
+        <v>80</v>
+      </c>
+      <c r="D107" s="37">
         <v>75</v>
       </c>
-      <c r="E107" s="24">
+      <c r="E107" s="20">
         <v>85</v>
       </c>
-      <c r="F107" s="39">
+      <c r="F107" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -3971,16 +3969,16 @@
       <c r="B108" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C108" s="24">
+      <c r="C108" s="20">
         <v>71</v>
       </c>
-      <c r="D108" s="41">
+      <c r="D108" s="37">
         <v>85</v>
       </c>
-      <c r="E108" s="24">
+      <c r="E108" s="20">
         <v>70</v>
       </c>
-      <c r="F108" s="39">
+      <c r="F108" s="35">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -3991,16 +3989,16 @@
       <c r="B109" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C109" s="24">
+      <c r="C109" s="20">
         <v>95</v>
       </c>
-      <c r="D109" s="41">
+      <c r="D109" s="37">
         <v>86</v>
       </c>
-      <c r="E109" s="24">
+      <c r="E109" s="20">
         <v>76</v>
       </c>
-      <c r="F109" s="39">
+      <c r="F109" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4011,16 +4009,16 @@
       <c r="B110" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C110" s="24">
+      <c r="C110" s="20">
         <v>92</v>
       </c>
-      <c r="D110" s="41">
+      <c r="D110" s="37">
         <v>86</v>
       </c>
-      <c r="E110" s="24">
+      <c r="E110" s="20">
         <v>51</v>
       </c>
-      <c r="F110" s="39">
+      <c r="F110" s="35">
         <v>84.21</v>
       </c>
     </row>
@@ -4031,16 +4029,16 @@
       <c r="B111" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C111" s="24">
-        <v>80</v>
-      </c>
-      <c r="D111" s="41">
+      <c r="C111" s="20">
+        <v>80</v>
+      </c>
+      <c r="D111" s="37">
         <v>75</v>
       </c>
-      <c r="E111" s="24">
+      <c r="E111" s="20">
         <v>63</v>
       </c>
-      <c r="F111" s="39">
+      <c r="F111" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4051,16 +4049,16 @@
       <c r="B112" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C112" s="24">
+      <c r="C112" s="20">
         <v>85</v>
       </c>
-      <c r="D112" s="41">
-        <v>80</v>
-      </c>
-      <c r="E112" s="24">
+      <c r="D112" s="37">
+        <v>80</v>
+      </c>
+      <c r="E112" s="20">
         <v>72</v>
       </c>
-      <c r="F112" s="39">
+      <c r="F112" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -4071,16 +4069,16 @@
       <c r="B113" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C113" s="24">
-        <v>80</v>
-      </c>
-      <c r="D113" s="41">
+      <c r="C113" s="20">
+        <v>80</v>
+      </c>
+      <c r="D113" s="37">
         <v>72</v>
       </c>
-      <c r="E113" s="24">
+      <c r="E113" s="20">
         <v>64</v>
       </c>
-      <c r="F113" s="39">
+      <c r="F113" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -4091,16 +4089,16 @@
       <c r="B114" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C114" s="24">
+      <c r="C114" s="20">
         <v>84</v>
       </c>
-      <c r="D114" s="41">
+      <c r="D114" s="37">
         <v>81</v>
       </c>
-      <c r="E114" s="24">
+      <c r="E114" s="20">
         <v>77</v>
       </c>
-      <c r="F114" s="39">
+      <c r="F114" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4111,16 +4109,16 @@
       <c r="B115" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C115" s="24">
+      <c r="C115" s="20">
         <v>89</v>
       </c>
-      <c r="D115" s="41">
+      <c r="D115" s="37">
         <v>82</v>
       </c>
-      <c r="E115" s="24">
+      <c r="E115" s="20">
         <v>69</v>
       </c>
-      <c r="F115" s="39">
+      <c r="F115" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -4131,16 +4129,16 @@
       <c r="B116" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="C116" s="24">
+      <c r="C116" s="20">
         <v>78</v>
       </c>
-      <c r="D116" s="41">
-        <v>80</v>
-      </c>
-      <c r="E116" s="24">
+      <c r="D116" s="37">
+        <v>80</v>
+      </c>
+      <c r="E116" s="20">
         <v>75</v>
       </c>
-      <c r="F116" s="39">
+      <c r="F116" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4151,16 +4149,16 @@
       <c r="B117" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C117" s="24">
-        <v>80</v>
-      </c>
-      <c r="D117" s="41">
+      <c r="C117" s="20">
+        <v>80</v>
+      </c>
+      <c r="D117" s="37">
         <v>82</v>
       </c>
-      <c r="E117" s="24">
+      <c r="E117" s="20">
         <v>92</v>
       </c>
-      <c r="F117" s="39">
+      <c r="F117" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -4171,16 +4169,16 @@
       <c r="B118" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C118" s="24">
+      <c r="C118" s="20">
         <v>87</v>
       </c>
-      <c r="D118" s="41">
+      <c r="D118" s="37">
         <v>84</v>
       </c>
-      <c r="E118" s="24">
+      <c r="E118" s="20">
         <v>74</v>
       </c>
-      <c r="F118" s="39">
+      <c r="F118" s="35">
         <v>57.14</v>
       </c>
     </row>
@@ -4191,16 +4189,16 @@
       <c r="B119" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C119" s="24">
+      <c r="C119" s="20">
         <v>83</v>
       </c>
-      <c r="D119" s="41">
+      <c r="D119" s="37">
         <v>72</v>
       </c>
-      <c r="E119" s="24">
+      <c r="E119" s="20">
         <v>82</v>
       </c>
-      <c r="F119" s="39">
+      <c r="F119" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4211,16 +4209,16 @@
       <c r="B120" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C120" s="24">
+      <c r="C120" s="20">
         <v>89</v>
       </c>
-      <c r="D120" s="41">
+      <c r="D120" s="37">
         <v>75</v>
       </c>
-      <c r="E120" s="24">
+      <c r="E120" s="20">
         <v>52</v>
       </c>
-      <c r="F120" s="39">
+      <c r="F120" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4231,16 +4229,16 @@
       <c r="B121" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C121" s="24">
+      <c r="C121" s="20">
         <v>94</v>
       </c>
-      <c r="D121" s="41">
+      <c r="D121" s="37">
         <v>85</v>
       </c>
-      <c r="E121" s="24">
-        <v>80</v>
-      </c>
-      <c r="F121" s="39">
+      <c r="E121" s="20">
+        <v>80</v>
+      </c>
+      <c r="F121" s="35">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -4251,16 +4249,16 @@
       <c r="B122" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C122" s="24">
-        <v>80</v>
-      </c>
-      <c r="D122" s="41">
+      <c r="C122" s="20">
+        <v>80</v>
+      </c>
+      <c r="D122" s="37">
         <v>75</v>
       </c>
-      <c r="E122" s="24">
+      <c r="E122" s="20">
         <v>33</v>
       </c>
-      <c r="F122" s="39">
+      <c r="F122" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -4271,16 +4269,16 @@
       <c r="B123" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="C123" s="24">
-        <v>80</v>
-      </c>
-      <c r="D123" s="41">
+      <c r="C123" s="20">
+        <v>80</v>
+      </c>
+      <c r="D123" s="37">
         <v>82</v>
       </c>
-      <c r="E123" s="24">
+      <c r="E123" s="20">
         <v>54</v>
       </c>
-      <c r="F123" s="39">
+      <c r="F123" s="35">
         <v>61.539999999999992</v>
       </c>
     </row>
@@ -4291,16 +4289,16 @@
       <c r="B124" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C124" s="24">
-        <v>80</v>
-      </c>
-      <c r="D124" s="41">
+      <c r="C124" s="20">
+        <v>80</v>
+      </c>
+      <c r="D124" s="37">
         <v>75</v>
       </c>
-      <c r="E124" s="24">
+      <c r="E124" s="20">
         <v>62</v>
       </c>
-      <c r="F124" s="39">
+      <c r="F124" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4311,16 +4309,16 @@
       <c r="B125" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C125" s="24">
+      <c r="C125" s="20">
         <v>85</v>
       </c>
-      <c r="D125" s="41">
+      <c r="D125" s="37">
         <v>78</v>
       </c>
-      <c r="E125" s="24">
+      <c r="E125" s="20">
         <v>62</v>
       </c>
-      <c r="F125" s="39">
+      <c r="F125" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4331,16 +4329,16 @@
       <c r="B126" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C126" s="24">
-        <v>80</v>
-      </c>
-      <c r="D126" s="41">
+      <c r="C126" s="20">
+        <v>80</v>
+      </c>
+      <c r="D126" s="37">
         <v>78</v>
       </c>
-      <c r="E126" s="24">
+      <c r="E126" s="20">
         <v>77</v>
       </c>
-      <c r="F126" s="39">
+      <c r="F126" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4351,16 +4349,16 @@
       <c r="B127" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C127" s="24">
+      <c r="C127" s="20">
         <v>88</v>
       </c>
-      <c r="D127" s="41">
-        <v>80</v>
-      </c>
-      <c r="E127" s="24">
+      <c r="D127" s="37">
+        <v>80</v>
+      </c>
+      <c r="E127" s="20">
         <v>62</v>
       </c>
-      <c r="F127" s="39">
+      <c r="F127" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4371,16 +4369,16 @@
       <c r="B128" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C128" s="24">
-        <v>80</v>
-      </c>
-      <c r="D128" s="41">
+      <c r="C128" s="20">
+        <v>80</v>
+      </c>
+      <c r="D128" s="37">
         <v>82</v>
       </c>
-      <c r="E128" s="24">
+      <c r="E128" s="20">
         <v>60</v>
       </c>
-      <c r="F128" s="39">
+      <c r="F128" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -4391,16 +4389,16 @@
       <c r="B129" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C129" s="24">
+      <c r="C129" s="20">
         <v>91</v>
       </c>
-      <c r="D129" s="41">
+      <c r="D129" s="37">
         <v>74</v>
       </c>
-      <c r="E129" s="24">
+      <c r="E129" s="20">
         <v>77</v>
       </c>
-      <c r="F129" s="39">
+      <c r="F129" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4411,16 +4409,16 @@
       <c r="B130" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="C130" s="24">
+      <c r="C130" s="20">
         <v>89</v>
       </c>
-      <c r="D130" s="41">
+      <c r="D130" s="37">
         <v>78</v>
       </c>
-      <c r="E130" s="24">
+      <c r="E130" s="20">
         <v>73</v>
       </c>
-      <c r="F130" s="39">
+      <c r="F130" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4431,16 +4429,16 @@
       <c r="B131" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="24">
+      <c r="C131" s="20">
         <v>88</v>
       </c>
-      <c r="D131" s="41">
+      <c r="D131" s="37">
         <v>72</v>
       </c>
-      <c r="E131" s="24">
+      <c r="E131" s="20">
         <v>48</v>
       </c>
-      <c r="F131" s="39">
+      <c r="F131" s="35">
         <v>61.9</v>
       </c>
     </row>
@@ -4451,16 +4449,16 @@
       <c r="B132" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="C132" s="24">
-        <v>80</v>
-      </c>
-      <c r="D132" s="41">
+      <c r="C132" s="20">
+        <v>80</v>
+      </c>
+      <c r="D132" s="37">
         <v>75</v>
       </c>
-      <c r="E132" s="24">
+      <c r="E132" s="20">
         <v>65</v>
       </c>
-      <c r="F132" s="39">
+      <c r="F132" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4471,16 +4469,16 @@
       <c r="B133" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="C133" s="24">
+      <c r="C133" s="20">
         <v>85</v>
       </c>
-      <c r="D133" s="41">
+      <c r="D133" s="37">
         <v>78</v>
       </c>
-      <c r="E133" s="24">
+      <c r="E133" s="20">
         <v>59</v>
       </c>
-      <c r="F133" s="39">
+      <c r="F133" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -4491,16 +4489,16 @@
       <c r="B134" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="C134" s="24">
+      <c r="C134" s="20">
         <v>92</v>
       </c>
-      <c r="D134" s="41">
-        <v>80</v>
-      </c>
-      <c r="E134" s="24">
+      <c r="D134" s="37">
+        <v>80</v>
+      </c>
+      <c r="E134" s="20">
         <v>59</v>
       </c>
-      <c r="F134" s="39">
+      <c r="F134" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4511,16 +4509,16 @@
       <c r="B135" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C135" s="24">
+      <c r="C135" s="20">
         <v>86</v>
       </c>
-      <c r="D135" s="41">
+      <c r="D135" s="37">
         <v>89</v>
       </c>
-      <c r="E135" s="24">
+      <c r="E135" s="20">
         <v>75</v>
       </c>
-      <c r="F135" s="39">
+      <c r="F135" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4531,16 +4529,16 @@
       <c r="B136" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C136" s="24">
+      <c r="C136" s="20">
         <v>85</v>
       </c>
-      <c r="D136" s="41">
+      <c r="D136" s="37">
         <v>74</v>
       </c>
-      <c r="E136" s="24">
+      <c r="E136" s="20">
         <v>50</v>
       </c>
-      <c r="F136" s="39">
+      <c r="F136" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4551,16 +4549,16 @@
       <c r="B137" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="C137" s="24">
+      <c r="C137" s="20">
         <v>95</v>
       </c>
-      <c r="D137" s="41">
+      <c r="D137" s="37">
         <v>89</v>
       </c>
-      <c r="E137" s="24">
+      <c r="E137" s="20">
         <v>59</v>
       </c>
-      <c r="F137" s="39">
+      <c r="F137" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4571,16 +4569,16 @@
       <c r="B138" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C138" s="24">
+      <c r="C138" s="20">
         <v>88</v>
       </c>
-      <c r="D138" s="41">
+      <c r="D138" s="37">
         <v>86</v>
       </c>
-      <c r="E138" s="24">
+      <c r="E138" s="20">
         <v>46</v>
       </c>
-      <c r="F138" s="39">
+      <c r="F138" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4591,16 +4589,16 @@
       <c r="B139" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C139" s="24">
+      <c r="C139" s="20">
         <v>93</v>
       </c>
-      <c r="D139" s="41">
+      <c r="D139" s="37">
         <v>86</v>
       </c>
-      <c r="E139" s="24">
-        <v>80</v>
-      </c>
-      <c r="F139" s="39">
+      <c r="E139" s="20">
+        <v>80</v>
+      </c>
+      <c r="F139" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4611,16 +4609,16 @@
       <c r="B140" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="C140" s="24">
+      <c r="C140" s="20">
         <v>75</v>
       </c>
-      <c r="D140" s="41">
+      <c r="D140" s="37">
         <v>85</v>
       </c>
-      <c r="E140" s="24">
-        <v>80</v>
-      </c>
-      <c r="F140" s="39">
+      <c r="E140" s="20">
+        <v>80</v>
+      </c>
+      <c r="F140" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4631,16 +4629,16 @@
       <c r="B141" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="C141" s="24">
+      <c r="C141" s="20">
         <v>88</v>
       </c>
-      <c r="D141" s="41">
-        <v>78</v>
-      </c>
-      <c r="E141" s="24">
+      <c r="D141" s="38">
+        <v>82</v>
+      </c>
+      <c r="E141" s="20">
         <v>40</v>
       </c>
-      <c r="F141" s="39">
+      <c r="F141" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -4651,16 +4649,16 @@
       <c r="B142" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="C142" s="24">
+      <c r="C142" s="20">
         <v>75</v>
       </c>
-      <c r="D142" s="41">
+      <c r="D142" s="37">
         <v>85</v>
       </c>
-      <c r="E142" s="24">
+      <c r="E142" s="20">
         <v>84</v>
       </c>
-      <c r="F142" s="39">
+      <c r="F142" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -4671,16 +4669,16 @@
       <c r="B143" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="C143" s="24">
-        <v>80</v>
-      </c>
-      <c r="D143" s="41">
+      <c r="C143" s="20">
+        <v>80</v>
+      </c>
+      <c r="D143" s="37">
         <v>79</v>
       </c>
-      <c r="E143" s="24">
+      <c r="E143" s="20">
         <v>82</v>
       </c>
-      <c r="F143" s="39">
+      <c r="F143" s="35">
         <v>85.71</v>
       </c>
     </row>
@@ -4691,16 +4689,16 @@
       <c r="B144" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C144" s="24">
+      <c r="C144" s="20">
         <v>89</v>
       </c>
-      <c r="D144" s="41">
+      <c r="D144" s="37">
         <v>74</v>
       </c>
-      <c r="E144" s="24">
+      <c r="E144" s="20">
         <v>66</v>
       </c>
-      <c r="F144" s="39">
+      <c r="F144" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4711,16 +4709,16 @@
       <c r="B145" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C145" s="24" t="s">
+      <c r="C145" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D145" s="41">
+      <c r="D145" s="37">
         <v>75</v>
       </c>
-      <c r="E145" s="24">
+      <c r="E145" s="20">
         <v>51</v>
       </c>
-      <c r="F145" s="39">
+      <c r="F145" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -4731,16 +4729,16 @@
       <c r="B146" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="C146" s="24">
+      <c r="C146" s="20">
         <v>79</v>
       </c>
-      <c r="D146" s="41">
+      <c r="D146" s="37">
         <v>75</v>
       </c>
-      <c r="E146" s="24">
+      <c r="E146" s="20">
         <v>69</v>
       </c>
-      <c r="F146" s="39">
+      <c r="F146" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4751,16 +4749,16 @@
       <c r="B147" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C147" s="24">
+      <c r="C147" s="20">
         <v>85</v>
       </c>
-      <c r="D147" s="41">
+      <c r="D147" s="37">
         <v>72</v>
       </c>
-      <c r="E147" s="24">
+      <c r="E147" s="20">
         <v>75</v>
       </c>
-      <c r="F147" s="39">
+      <c r="F147" s="35">
         <v>90</v>
       </c>
     </row>
@@ -4771,16 +4769,16 @@
       <c r="B148" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C148" s="24">
+      <c r="C148" s="20">
         <v>90</v>
       </c>
-      <c r="D148" s="41">
-        <v>80</v>
-      </c>
-      <c r="E148" s="24">
+      <c r="D148" s="37">
+        <v>80</v>
+      </c>
+      <c r="E148" s="20">
         <v>58</v>
       </c>
-      <c r="F148" s="39">
+      <c r="F148" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4791,16 +4789,16 @@
       <c r="B149" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="C149" s="24">
-        <v>80</v>
-      </c>
-      <c r="D149" s="41">
+      <c r="C149" s="20">
+        <v>80</v>
+      </c>
+      <c r="D149" s="37">
         <v>79</v>
       </c>
-      <c r="E149" s="24">
+      <c r="E149" s="20">
         <v>75</v>
       </c>
-      <c r="F149" s="39">
+      <c r="F149" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4811,16 +4809,16 @@
       <c r="B150" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="C150" s="24">
-        <v>80</v>
-      </c>
-      <c r="D150" s="41">
+      <c r="C150" s="20">
+        <v>80</v>
+      </c>
+      <c r="D150" s="37">
         <v>81</v>
       </c>
-      <c r="E150" s="24">
+      <c r="E150" s="20">
         <v>62</v>
       </c>
-      <c r="F150" s="39">
+      <c r="F150" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4831,16 +4829,16 @@
       <c r="B151" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C151" s="24">
+      <c r="C151" s="20">
         <v>87</v>
       </c>
-      <c r="D151" s="41">
+      <c r="D151" s="37">
         <v>72</v>
       </c>
-      <c r="E151" s="24">
+      <c r="E151" s="20">
         <v>93</v>
       </c>
-      <c r="F151" s="39">
+      <c r="F151" s="35">
         <v>76.19</v>
       </c>
     </row>
@@ -4851,16 +4849,16 @@
       <c r="B152" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="C152" s="24">
+      <c r="C152" s="20">
         <v>85</v>
       </c>
-      <c r="D152" s="41">
+      <c r="D152" s="37">
         <v>74</v>
       </c>
-      <c r="E152" s="24">
+      <c r="E152" s="20">
         <v>71</v>
       </c>
-      <c r="F152" s="39">
+      <c r="F152" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4871,16 +4869,16 @@
       <c r="B153" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="C153" s="24">
+      <c r="C153" s="20">
         <v>81</v>
       </c>
-      <c r="D153" s="41">
+      <c r="D153" s="37">
         <v>81</v>
       </c>
-      <c r="E153" s="24">
+      <c r="E153" s="20">
         <v>91</v>
       </c>
-      <c r="F153" s="39">
+      <c r="F153" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4891,16 +4889,16 @@
       <c r="B154" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="C154" s="24">
+      <c r="C154" s="20">
         <v>88</v>
       </c>
-      <c r="D154" s="41">
+      <c r="D154" s="37">
         <v>72</v>
       </c>
-      <c r="E154" s="24">
+      <c r="E154" s="20">
         <v>88</v>
       </c>
-      <c r="F154" s="39">
+      <c r="F154" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -4911,16 +4909,16 @@
       <c r="B155" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="C155" s="24">
+      <c r="C155" s="20">
         <v>88</v>
       </c>
-      <c r="D155" s="41">
-        <v>80</v>
-      </c>
-      <c r="E155" s="24">
+      <c r="D155" s="37">
+        <v>80</v>
+      </c>
+      <c r="E155" s="20">
         <v>65</v>
       </c>
-      <c r="F155" s="39">
+      <c r="F155" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4931,16 +4929,16 @@
       <c r="B156" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="C156" s="24">
+      <c r="C156" s="20">
         <v>85</v>
       </c>
-      <c r="D156" s="41">
+      <c r="D156" s="37">
         <v>82</v>
       </c>
-      <c r="E156" s="24">
+      <c r="E156" s="20">
         <v>83</v>
       </c>
-      <c r="F156" s="39">
+      <c r="F156" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -4951,16 +4949,16 @@
       <c r="B157" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C157" s="24">
+      <c r="C157" s="20">
         <v>88</v>
       </c>
-      <c r="D157" s="41">
+      <c r="D157" s="37">
         <v>79</v>
       </c>
-      <c r="E157" s="24">
+      <c r="E157" s="20">
         <v>64</v>
       </c>
-      <c r="F157" s="39">
+      <c r="F157" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4971,16 +4969,16 @@
       <c r="B158" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C158" s="24">
+      <c r="C158" s="20">
         <v>81</v>
       </c>
-      <c r="D158" s="41">
+      <c r="D158" s="37">
         <v>78</v>
       </c>
-      <c r="E158" s="24">
+      <c r="E158" s="20">
         <v>68</v>
       </c>
-      <c r="F158" s="39">
+      <c r="F158" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -4991,16 +4989,16 @@
       <c r="B159" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C159" s="24">
+      <c r="C159" s="20">
         <v>91</v>
       </c>
-      <c r="D159" s="41">
+      <c r="D159" s="37">
         <v>74</v>
       </c>
-      <c r="E159" s="24">
+      <c r="E159" s="20">
         <v>68</v>
       </c>
-      <c r="F159" s="39">
+      <c r="F159" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -5011,16 +5009,16 @@
       <c r="B160" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C160" s="24">
+      <c r="C160" s="20">
         <v>86</v>
       </c>
-      <c r="D160" s="41">
+      <c r="D160" s="37">
         <v>78</v>
       </c>
-      <c r="E160" s="24">
+      <c r="E160" s="20">
         <v>85</v>
       </c>
-      <c r="F160" s="39">
+      <c r="F160" s="35">
         <v>95.240000000000009</v>
       </c>
     </row>
@@ -5031,16 +5029,16 @@
       <c r="B161" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="C161" s="24">
-        <v>80</v>
-      </c>
-      <c r="D161" s="41">
+      <c r="C161" s="20">
+        <v>80</v>
+      </c>
+      <c r="D161" s="37">
         <v>75</v>
       </c>
-      <c r="E161" s="24">
+      <c r="E161" s="20">
         <v>54</v>
       </c>
-      <c r="F161" s="39">
+      <c r="F161" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -5051,16 +5049,16 @@
       <c r="B162" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="C162" s="24">
+      <c r="C162" s="20">
         <v>94</v>
       </c>
-      <c r="D162" s="41">
-        <v>80</v>
-      </c>
-      <c r="E162" s="24">
+      <c r="D162" s="37">
+        <v>80</v>
+      </c>
+      <c r="E162" s="20">
         <v>54</v>
       </c>
-      <c r="F162" s="39">
+      <c r="F162" s="35">
         <v>90.48</v>
       </c>
     </row>
@@ -5071,16 +5069,16 @@
       <c r="B163" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="C163" s="24">
+      <c r="C163" s="20">
         <v>78</v>
       </c>
-      <c r="D163" s="41">
+      <c r="D163" s="37">
         <v>72</v>
       </c>
-      <c r="E163" s="24">
+      <c r="E163" s="20">
         <v>60</v>
       </c>
-      <c r="F163" s="39">
+      <c r="F163" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -5091,16 +5089,16 @@
       <c r="B164" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="C164" s="24">
+      <c r="C164" s="20">
         <v>87</v>
       </c>
-      <c r="D164" s="41">
+      <c r="D164" s="37">
         <v>84</v>
       </c>
-      <c r="E164" s="24">
+      <c r="E164" s="20">
         <v>59</v>
       </c>
-      <c r="F164" s="40">
+      <c r="F164" s="36">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -5111,16 +5109,16 @@
       <c r="B165" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="C165" s="24">
+      <c r="C165" s="20">
         <v>85</v>
       </c>
-      <c r="D165" s="41">
+      <c r="D165" s="37">
         <v>78</v>
       </c>
-      <c r="E165" s="24">
+      <c r="E165" s="20">
         <v>81</v>
       </c>
-      <c r="F165" s="40">
+      <c r="F165" s="36">
         <v>76.19</v>
       </c>
     </row>
@@ -5131,16 +5129,16 @@
       <c r="B166" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="C166" s="24">
-        <v>80</v>
-      </c>
-      <c r="D166" s="41">
+      <c r="C166" s="20">
+        <v>80</v>
+      </c>
+      <c r="D166" s="37">
         <v>81</v>
       </c>
-      <c r="E166" s="24">
+      <c r="E166" s="20">
         <v>87</v>
       </c>
-      <c r="F166" s="40">
+      <c r="F166" s="36">
         <v>80.95</v>
       </c>
     </row>
@@ -5151,16 +5149,16 @@
       <c r="B167" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="C167" s="24">
+      <c r="C167" s="20">
         <v>90</v>
       </c>
-      <c r="D167" s="41">
+      <c r="D167" s="37">
         <v>81</v>
       </c>
-      <c r="E167" s="24">
+      <c r="E167" s="20">
         <v>90</v>
       </c>
-      <c r="F167" s="40">
+      <c r="F167" s="36">
         <v>80.95</v>
       </c>
     </row>
@@ -5171,16 +5169,16 @@
       <c r="B168" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="C168" s="24">
-        <v>80</v>
-      </c>
-      <c r="D168" s="41">
+      <c r="C168" s="20">
+        <v>80</v>
+      </c>
+      <c r="D168" s="37">
         <v>91</v>
       </c>
-      <c r="E168" s="24">
+      <c r="E168" s="20">
         <v>59</v>
       </c>
-      <c r="F168" s="40">
+      <c r="F168" s="36">
         <v>90.48</v>
       </c>
     </row>
@@ -5191,16 +5189,16 @@
       <c r="B169" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C169" s="24">
-        <v>80</v>
-      </c>
-      <c r="D169" s="41">
+      <c r="C169" s="20">
+        <v>80</v>
+      </c>
+      <c r="D169" s="37">
         <v>78</v>
       </c>
-      <c r="E169" s="24">
+      <c r="E169" s="20">
         <v>59</v>
       </c>
-      <c r="F169" s="40">
+      <c r="F169" s="36">
         <v>66.67</v>
       </c>
     </row>
@@ -5211,54 +5209,54 @@
       <c r="B170" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="C170" s="24">
+      <c r="C170" s="20">
         <v>82</v>
       </c>
-      <c r="D170" s="41">
+      <c r="D170" s="37">
         <v>89</v>
       </c>
-      <c r="E170" s="24">
+      <c r="E170" s="20">
         <v>46</v>
       </c>
-      <c r="F170" s="40">
+      <c r="F170" s="36">
         <v>76.19</v>
       </c>
     </row>
     <row r="171" spans="1:6">
-      <c r="A171" s="20" t="s">
+      <c r="A171" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="B171" s="21" t="s">
+      <c r="B171" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="C171" s="22">
+      <c r="C171" s="20">
         <v>50</v>
       </c>
-      <c r="D171" s="41"/>
-      <c r="E171" s="24" t="s">
+      <c r="D171" s="37"/>
+      <c r="E171" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F171" s="40">
+      <c r="F171" s="36">
         <v>14.29</v>
       </c>
     </row>
     <row r="172" spans="1:6">
-      <c r="A172" s="23" t="s">
+      <c r="A172" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="B172" s="21" t="s">
+      <c r="B172" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="C172" s="22">
+      <c r="C172" s="20">
         <v>50</v>
       </c>
-      <c r="D172" s="41">
+      <c r="D172" s="37">
         <v>91</v>
       </c>
-      <c r="E172" s="24">
+      <c r="E172" s="20">
         <v>55</v>
       </c>
-      <c r="F172" s="40">
+      <c r="F172" s="36">
         <v>76.19</v>
       </c>
     </row>
@@ -5269,16 +5267,16 @@
       <c r="B173" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="C173" s="24">
+      <c r="C173" s="20">
         <v>60</v>
       </c>
-      <c r="D173" s="41">
+      <c r="D173" s="37">
         <v>91</v>
       </c>
-      <c r="E173" s="24">
+      <c r="E173" s="20">
         <v>71</v>
       </c>
-      <c r="F173" s="40">
+      <c r="F173" s="36">
         <v>90.48</v>
       </c>
     </row>
@@ -5289,16 +5287,16 @@
       <c r="B174" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="C174" s="24">
+      <c r="C174" s="20">
         <v>75</v>
       </c>
-      <c r="D174" s="41">
+      <c r="D174" s="37">
         <v>91</v>
       </c>
-      <c r="E174" s="24">
+      <c r="E174" s="20">
         <v>67</v>
       </c>
-      <c r="F174" s="40">
+      <c r="F174" s="36">
         <v>80.95</v>
       </c>
     </row>
@@ -5309,16 +5307,16 @@
       <c r="B175" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="C175" s="24">
+      <c r="C175" s="20">
         <v>78</v>
       </c>
-      <c r="D175" s="41">
+      <c r="D175" s="37">
         <v>91</v>
       </c>
-      <c r="E175" s="24">
+      <c r="E175" s="20">
         <v>57</v>
       </c>
-      <c r="F175" s="40">
+      <c r="F175" s="36">
         <v>85.71</v>
       </c>
     </row>
@@ -5329,16 +5327,16 @@
       <c r="B176" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="C176" s="24">
+      <c r="C176" s="20">
         <v>79</v>
       </c>
-      <c r="D176" s="41">
+      <c r="D176" s="37">
         <v>85</v>
       </c>
-      <c r="E176" s="24">
+      <c r="E176" s="20">
         <v>54</v>
       </c>
-      <c r="F176" s="40">
+      <c r="F176" s="36">
         <v>66.67</v>
       </c>
     </row>
@@ -5349,14 +5347,16 @@
       <c r="B177" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="C177" s="24">
-        <v>80</v>
-      </c>
-      <c r="D177" s="41"/>
-      <c r="E177" s="24">
+      <c r="C177" s="20">
+        <v>80</v>
+      </c>
+      <c r="D177" s="38">
+        <v>78</v>
+      </c>
+      <c r="E177" s="20">
         <v>69</v>
       </c>
-      <c r="F177" s="40">
+      <c r="F177" s="36">
         <v>76.19</v>
       </c>
     </row>
@@ -5367,16 +5367,16 @@
       <c r="B178" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="C178" s="24">
+      <c r="C178" s="20">
         <v>50</v>
       </c>
-      <c r="D178" s="41">
+      <c r="D178" s="37">
         <v>91</v>
       </c>
-      <c r="E178" s="24">
+      <c r="E178" s="20">
         <v>56</v>
       </c>
-      <c r="F178" s="40">
+      <c r="F178" s="36">
         <v>90.48</v>
       </c>
     </row>
@@ -5387,16 +5387,16 @@
       <c r="B179" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="C179" s="24">
-        <v>80</v>
-      </c>
-      <c r="D179" s="41">
+      <c r="C179" s="20">
+        <v>80</v>
+      </c>
+      <c r="D179" s="37">
         <v>91</v>
       </c>
-      <c r="E179" s="24">
+      <c r="E179" s="20">
         <v>54</v>
       </c>
-      <c r="F179" s="40">
+      <c r="F179" s="36">
         <v>85.71</v>
       </c>
     </row>
@@ -5407,16 +5407,16 @@
       <c r="B180" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="C180" s="24">
-        <v>80</v>
-      </c>
-      <c r="D180" s="41">
+      <c r="C180" s="20">
+        <v>80</v>
+      </c>
+      <c r="D180" s="37">
         <v>78</v>
       </c>
-      <c r="E180" s="24">
+      <c r="E180" s="20">
         <v>57</v>
       </c>
-      <c r="F180" s="40">
+      <c r="F180" s="36">
         <v>76.19</v>
       </c>
     </row>
@@ -5427,16 +5427,16 @@
       <c r="B181" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="C181" s="24">
+      <c r="C181" s="20">
         <v>50</v>
       </c>
-      <c r="D181" s="41">
+      <c r="D181" s="37">
         <v>91</v>
       </c>
-      <c r="E181" s="24">
+      <c r="E181" s="20">
         <v>39</v>
       </c>
-      <c r="F181" s="40">
+      <c r="F181" s="36">
         <v>71.430000000000007</v>
       </c>
     </row>
@@ -5447,16 +5447,16 @@
       <c r="B182" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="C182" s="24">
+      <c r="C182" s="20">
         <v>85</v>
       </c>
-      <c r="D182" s="41">
+      <c r="D182" s="37">
         <v>85</v>
       </c>
-      <c r="E182" s="24">
+      <c r="E182" s="20">
         <v>52</v>
       </c>
-      <c r="F182" s="40">
+      <c r="F182" s="36">
         <v>76.19</v>
       </c>
     </row>
@@ -5467,14 +5467,16 @@
       <c r="B183" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="C183" s="24">
+      <c r="C183" s="20">
         <v>87</v>
       </c>
-      <c r="D183" s="41"/>
-      <c r="E183" s="24">
+      <c r="D183" s="38">
+        <v>80</v>
+      </c>
+      <c r="E183" s="20">
         <v>57</v>
       </c>
-      <c r="F183" s="39">
+      <c r="F183" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -5485,16 +5487,16 @@
       <c r="B184" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="C184" s="24">
+      <c r="C184" s="20">
         <v>85</v>
       </c>
-      <c r="D184" s="41">
+      <c r="D184" s="37">
         <v>84</v>
       </c>
-      <c r="E184" s="24">
+      <c r="E184" s="20">
         <v>69</v>
       </c>
-      <c r="F184" s="39">
+      <c r="F184" s="35">
         <v>80.95</v>
       </c>
     </row>
@@ -5505,426 +5507,426 @@
       <c r="B185" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="C185" s="24">
+      <c r="C185" s="20">
         <v>85</v>
       </c>
-      <c r="D185" s="41">
-        <v>80</v>
-      </c>
-      <c r="E185" s="24">
+      <c r="D185" s="37">
+        <v>80</v>
+      </c>
+      <c r="E185" s="20">
         <v>58</v>
       </c>
-      <c r="F185" s="39">
+      <c r="F185" s="35">
         <v>80.95</v>
       </c>
     </row>
     <row r="186" spans="1:6">
-      <c r="A186" s="26" t="s">
+      <c r="A186" s="22" t="s">
         <v>372</v>
       </c>
-      <c r="B186" s="25" t="s">
+      <c r="B186" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="C186" s="24" t="s">
+      <c r="C186" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D186" s="41"/>
-      <c r="E186" s="24">
+      <c r="D186" s="37"/>
+      <c r="E186" s="20">
         <v>54</v>
       </c>
-      <c r="F186" s="39">
+      <c r="F186" s="35">
         <v>38.1</v>
       </c>
     </row>
     <row r="187" spans="1:6">
-      <c r="A187" s="26" t="s">
+      <c r="A187" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="B187" s="25" t="s">
+      <c r="B187" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="C187" s="24">
-        <v>80</v>
-      </c>
-      <c r="D187" s="41">
-        <v>80</v>
-      </c>
-      <c r="E187" s="24">
+      <c r="C187" s="20">
+        <v>80</v>
+      </c>
+      <c r="D187" s="37">
+        <v>80</v>
+      </c>
+      <c r="E187" s="20">
         <v>76</v>
       </c>
-      <c r="F187" s="39">
+      <c r="F187" s="35">
         <v>44.440000000000005</v>
       </c>
     </row>
     <row r="188" spans="1:6">
-      <c r="A188" s="26" t="s">
+      <c r="A188" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="B188" s="25"/>
-      <c r="C188" s="24"/>
-      <c r="D188" s="41"/>
-      <c r="E188" s="24">
+      <c r="B188" s="21"/>
+      <c r="C188" s="20"/>
+      <c r="D188" s="37"/>
+      <c r="E188" s="20">
         <v>63</v>
       </c>
-      <c r="F188" s="39">
+      <c r="F188" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="26" t="s">
+      <c r="A189" s="22" t="s">
         <v>380</v>
       </c>
-      <c r="B189" s="25"/>
-      <c r="C189" s="24"/>
-      <c r="D189" s="41"/>
-      <c r="E189" s="24">
+      <c r="B189" s="21"/>
+      <c r="C189" s="20"/>
+      <c r="D189" s="37"/>
+      <c r="E189" s="20">
         <v>26</v>
       </c>
-      <c r="F189" s="39">
+      <c r="F189" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:6">
-      <c r="A190" s="26" t="s">
+      <c r="A190" s="22" t="s">
         <v>381</v>
       </c>
-      <c r="B190" s="25"/>
-      <c r="C190" s="24"/>
-      <c r="D190" s="41"/>
-      <c r="E190" s="24">
+      <c r="B190" s="21"/>
+      <c r="C190" s="20"/>
+      <c r="D190" s="37"/>
+      <c r="E190" s="20">
         <v>31</v>
       </c>
-      <c r="F190" s="39">
+      <c r="F190" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="A191" s="28"/>
-      <c r="B191" s="29"/>
+      <c r="A191" s="24"/>
+      <c r="B191" s="25"/>
       <c r="C191" s="4"/>
       <c r="D191" s="5"/>
       <c r="E191" s="4"/>
-      <c r="F191" s="33"/>
+      <c r="F191" s="29"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="A192" s="28"/>
-      <c r="B192" s="29"/>
+      <c r="A192" s="24"/>
+      <c r="B192" s="25"/>
       <c r="C192" s="4"/>
       <c r="D192" s="5"/>
       <c r="E192" s="4"/>
-      <c r="F192" s="33"/>
+      <c r="F192" s="29"/>
     </row>
     <row r="193" spans="1:6">
-      <c r="A193" s="30"/>
-      <c r="B193" s="29"/>
+      <c r="A193" s="26"/>
+      <c r="B193" s="25"/>
       <c r="C193" s="4"/>
       <c r="D193" s="5"/>
       <c r="E193" s="4"/>
-      <c r="F193" s="33"/>
+      <c r="F193" s="29"/>
     </row>
     <row r="194" spans="1:6">
-      <c r="A194" s="30"/>
-      <c r="B194" s="29"/>
+      <c r="A194" s="26"/>
+      <c r="B194" s="25"/>
       <c r="C194" s="4"/>
       <c r="D194" s="5"/>
       <c r="E194" s="4"/>
-      <c r="F194" s="33"/>
+      <c r="F194" s="29"/>
     </row>
     <row r="195" spans="1:6">
-      <c r="A195" s="28"/>
-      <c r="B195" s="29"/>
+      <c r="A195" s="24"/>
+      <c r="B195" s="25"/>
       <c r="C195" s="6"/>
       <c r="D195" s="5"/>
       <c r="E195" s="4"/>
-      <c r="F195" s="33"/>
+      <c r="F195" s="29"/>
     </row>
     <row r="196" spans="1:6">
-      <c r="A196" s="28"/>
-      <c r="B196" s="29"/>
+      <c r="A196" s="24"/>
+      <c r="B196" s="25"/>
       <c r="C196" s="6"/>
       <c r="D196" s="5"/>
       <c r="E196" s="4"/>
-      <c r="F196" s="33"/>
+      <c r="F196" s="29"/>
     </row>
     <row r="197" spans="1:6">
-      <c r="A197" s="28"/>
-      <c r="B197" s="29"/>
+      <c r="A197" s="24"/>
+      <c r="B197" s="25"/>
       <c r="C197" s="6"/>
       <c r="D197" s="5"/>
       <c r="E197" s="4"/>
-      <c r="F197" s="33"/>
+      <c r="F197" s="29"/>
     </row>
     <row r="198" spans="1:6">
-      <c r="A198" s="28"/>
-      <c r="B198" s="29"/>
+      <c r="A198" s="24"/>
+      <c r="B198" s="25"/>
       <c r="C198" s="6"/>
       <c r="D198" s="5"/>
       <c r="E198" s="4"/>
-      <c r="F198" s="33"/>
+      <c r="F198" s="29"/>
     </row>
     <row r="199" spans="1:6">
-      <c r="A199" s="28"/>
-      <c r="B199" s="29"/>
+      <c r="A199" s="24"/>
+      <c r="B199" s="25"/>
       <c r="C199" s="6"/>
       <c r="D199" s="5"/>
       <c r="E199" s="4"/>
-      <c r="F199" s="33"/>
+      <c r="F199" s="29"/>
     </row>
     <row r="200" spans="1:6">
-      <c r="A200" s="28"/>
-      <c r="B200" s="29"/>
+      <c r="A200" s="24"/>
+      <c r="B200" s="25"/>
       <c r="C200" s="6"/>
       <c r="D200" s="5"/>
       <c r="E200" s="4"/>
-      <c r="F200" s="33"/>
+      <c r="F200" s="29"/>
     </row>
     <row r="201" spans="1:6">
-      <c r="A201" s="31"/>
-      <c r="B201" s="32"/>
+      <c r="A201" s="27"/>
+      <c r="B201" s="28"/>
       <c r="C201" s="6"/>
       <c r="D201" s="5"/>
       <c r="E201" s="4"/>
-      <c r="F201" s="33"/>
+      <c r="F201" s="29"/>
     </row>
     <row r="202" spans="1:6">
-      <c r="A202" s="31"/>
-      <c r="B202" s="32"/>
+      <c r="A202" s="27"/>
+      <c r="B202" s="28"/>
       <c r="C202" s="6"/>
       <c r="D202" s="5"/>
       <c r="E202" s="4"/>
-      <c r="F202" s="33"/>
+      <c r="F202" s="29"/>
     </row>
     <row r="203" spans="1:6">
-      <c r="A203" s="31"/>
-      <c r="B203" s="32"/>
+      <c r="A203" s="27"/>
+      <c r="B203" s="28"/>
       <c r="C203" s="6"/>
       <c r="D203" s="5"/>
       <c r="E203" s="4"/>
-      <c r="F203" s="33"/>
+      <c r="F203" s="29"/>
     </row>
     <row r="204" spans="1:6">
-      <c r="A204" s="31"/>
-      <c r="B204" s="32"/>
+      <c r="A204" s="27"/>
+      <c r="B204" s="28"/>
       <c r="C204" s="6"/>
       <c r="D204" s="5"/>
       <c r="E204" s="4"/>
-      <c r="F204" s="33"/>
+      <c r="F204" s="29"/>
     </row>
     <row r="205" spans="1:6">
-      <c r="A205" s="31"/>
-      <c r="B205" s="32"/>
+      <c r="A205" s="27"/>
+      <c r="B205" s="28"/>
       <c r="C205" s="6"/>
       <c r="D205" s="5"/>
       <c r="E205" s="4"/>
-      <c r="F205" s="33"/>
+      <c r="F205" s="29"/>
     </row>
     <row r="206" spans="1:6">
-      <c r="A206" s="31"/>
-      <c r="B206" s="32"/>
+      <c r="A206" s="27"/>
+      <c r="B206" s="28"/>
       <c r="C206" s="6"/>
       <c r="D206" s="5"/>
       <c r="E206" s="4"/>
-      <c r="F206" s="33"/>
+      <c r="F206" s="29"/>
     </row>
     <row r="207" spans="1:6">
-      <c r="A207" s="31"/>
-      <c r="B207" s="32"/>
+      <c r="A207" s="27"/>
+      <c r="B207" s="28"/>
       <c r="C207" s="6"/>
       <c r="D207" s="5"/>
       <c r="E207" s="4"/>
-      <c r="F207" s="33"/>
+      <c r="F207" s="29"/>
     </row>
     <row r="208" spans="1:6">
-      <c r="A208" s="31"/>
-      <c r="B208" s="32"/>
+      <c r="A208" s="27"/>
+      <c r="B208" s="28"/>
       <c r="C208" s="6"/>
       <c r="D208" s="5"/>
       <c r="E208" s="4"/>
-      <c r="F208" s="33"/>
+      <c r="F208" s="29"/>
     </row>
     <row r="209" spans="1:6">
-      <c r="A209" s="31"/>
-      <c r="B209" s="32"/>
+      <c r="A209" s="27"/>
+      <c r="B209" s="28"/>
       <c r="C209" s="6"/>
       <c r="D209" s="5"/>
       <c r="E209" s="4"/>
-      <c r="F209" s="33"/>
+      <c r="F209" s="29"/>
     </row>
     <row r="210" spans="1:6">
-      <c r="A210" s="31"/>
-      <c r="B210" s="32"/>
+      <c r="A210" s="27"/>
+      <c r="B210" s="28"/>
       <c r="C210" s="6"/>
       <c r="D210" s="5"/>
       <c r="E210" s="4"/>
-      <c r="F210" s="33"/>
+      <c r="F210" s="29"/>
     </row>
     <row r="211" spans="1:6">
-      <c r="A211" s="31"/>
-      <c r="B211" s="32"/>
+      <c r="A211" s="27"/>
+      <c r="B211" s="28"/>
       <c r="C211" s="6"/>
       <c r="D211" s="5"/>
       <c r="E211" s="4"/>
-      <c r="F211" s="33"/>
+      <c r="F211" s="29"/>
     </row>
     <row r="212" spans="1:6">
-      <c r="A212" s="31"/>
-      <c r="B212" s="32"/>
+      <c r="A212" s="27"/>
+      <c r="B212" s="28"/>
       <c r="C212" s="6"/>
       <c r="D212" s="5"/>
       <c r="E212" s="4"/>
-      <c r="F212" s="33"/>
+      <c r="F212" s="29"/>
     </row>
     <row r="213" spans="1:6">
-      <c r="A213" s="31"/>
-      <c r="B213" s="32"/>
+      <c r="A213" s="27"/>
+      <c r="B213" s="28"/>
       <c r="C213" s="6"/>
       <c r="D213" s="5"/>
       <c r="E213" s="4"/>
-      <c r="F213" s="33"/>
+      <c r="F213" s="29"/>
     </row>
     <row r="214" spans="1:6">
-      <c r="A214" s="31"/>
-      <c r="B214" s="32"/>
+      <c r="A214" s="27"/>
+      <c r="B214" s="28"/>
       <c r="C214" s="6"/>
       <c r="D214" s="5"/>
       <c r="E214" s="4"/>
-      <c r="F214" s="33"/>
+      <c r="F214" s="29"/>
     </row>
     <row r="215" spans="1:6">
-      <c r="A215" s="31"/>
-      <c r="B215" s="32"/>
+      <c r="A215" s="27"/>
+      <c r="B215" s="28"/>
       <c r="C215" s="6"/>
       <c r="D215" s="5"/>
       <c r="E215" s="4"/>
-      <c r="F215" s="33"/>
+      <c r="F215" s="29"/>
     </row>
     <row r="216" spans="1:6">
-      <c r="A216" s="31"/>
-      <c r="B216" s="32"/>
+      <c r="A216" s="27"/>
+      <c r="B216" s="28"/>
       <c r="C216" s="6"/>
       <c r="D216" s="5"/>
       <c r="E216" s="4"/>
-      <c r="F216" s="33"/>
+      <c r="F216" s="29"/>
     </row>
     <row r="217" spans="1:6">
-      <c r="A217" s="31"/>
-      <c r="B217" s="32"/>
+      <c r="A217" s="27"/>
+      <c r="B217" s="28"/>
       <c r="C217" s="6"/>
       <c r="D217" s="5"/>
       <c r="E217" s="4"/>
-      <c r="F217" s="33"/>
+      <c r="F217" s="29"/>
     </row>
     <row r="218" spans="1:6">
-      <c r="A218" s="31"/>
-      <c r="B218" s="32"/>
+      <c r="A218" s="27"/>
+      <c r="B218" s="28"/>
       <c r="C218" s="6"/>
       <c r="D218" s="5"/>
       <c r="E218" s="4"/>
-      <c r="F218" s="33"/>
+      <c r="F218" s="29"/>
     </row>
     <row r="219" spans="1:6">
-      <c r="A219" s="31"/>
-      <c r="B219" s="32"/>
+      <c r="A219" s="27"/>
+      <c r="B219" s="28"/>
       <c r="C219" s="6"/>
       <c r="D219" s="5"/>
       <c r="E219" s="4"/>
-      <c r="F219" s="33"/>
+      <c r="F219" s="29"/>
     </row>
     <row r="220" spans="1:6">
-      <c r="A220" s="31"/>
-      <c r="B220" s="32"/>
+      <c r="A220" s="27"/>
+      <c r="B220" s="28"/>
       <c r="C220" s="6"/>
       <c r="D220" s="5"/>
       <c r="E220" s="4"/>
-      <c r="F220" s="33"/>
+      <c r="F220" s="29"/>
     </row>
     <row r="221" spans="1:6">
-      <c r="A221" s="31"/>
-      <c r="B221" s="32"/>
+      <c r="A221" s="27"/>
+      <c r="B221" s="28"/>
       <c r="C221" s="6"/>
       <c r="D221" s="5"/>
       <c r="E221" s="4"/>
-      <c r="F221" s="33"/>
+      <c r="F221" s="29"/>
     </row>
     <row r="222" spans="1:6">
-      <c r="A222" s="31"/>
-      <c r="B222" s="32"/>
+      <c r="A222" s="27"/>
+      <c r="B222" s="28"/>
       <c r="C222" s="6"/>
       <c r="D222" s="5"/>
       <c r="E222" s="4"/>
-      <c r="F222" s="33"/>
+      <c r="F222" s="29"/>
     </row>
     <row r="223" spans="1:6">
-      <c r="A223" s="31"/>
-      <c r="B223" s="32"/>
+      <c r="A223" s="27"/>
+      <c r="B223" s="28"/>
       <c r="C223" s="6"/>
       <c r="D223" s="5"/>
       <c r="E223" s="4"/>
-      <c r="F223" s="33"/>
+      <c r="F223" s="29"/>
     </row>
     <row r="224" spans="1:6">
-      <c r="A224" s="31"/>
-      <c r="B224" s="32"/>
+      <c r="A224" s="27"/>
+      <c r="B224" s="28"/>
       <c r="C224" s="6"/>
       <c r="D224" s="5"/>
       <c r="E224" s="4"/>
-      <c r="F224" s="33"/>
+      <c r="F224" s="29"/>
     </row>
     <row r="225" spans="1:6">
-      <c r="A225" s="31"/>
-      <c r="B225" s="32"/>
+      <c r="A225" s="27"/>
+      <c r="B225" s="28"/>
       <c r="C225" s="6"/>
       <c r="D225" s="5"/>
       <c r="E225" s="4"/>
-      <c r="F225" s="33"/>
+      <c r="F225" s="29"/>
     </row>
     <row r="226" spans="1:6">
-      <c r="A226" s="31"/>
-      <c r="B226" s="32"/>
+      <c r="A226" s="27"/>
+      <c r="B226" s="28"/>
       <c r="C226" s="6"/>
       <c r="D226" s="5"/>
       <c r="E226" s="4"/>
-      <c r="F226" s="33"/>
+      <c r="F226" s="29"/>
     </row>
     <row r="227" spans="1:6">
-      <c r="A227" s="34"/>
-      <c r="B227" s="35"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="31"/>
       <c r="C227" s="6"/>
       <c r="D227" s="5"/>
       <c r="E227" s="4"/>
-      <c r="F227" s="33"/>
+      <c r="F227" s="29"/>
     </row>
     <row r="228" spans="1:6">
-      <c r="A228" s="34"/>
-      <c r="B228" s="35"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="31"/>
       <c r="C228" s="6"/>
       <c r="D228" s="5"/>
       <c r="E228" s="4"/>
-      <c r="F228" s="33"/>
+      <c r="F228" s="29"/>
     </row>
     <row r="229" spans="1:6">
-      <c r="A229" s="34"/>
-      <c r="B229" s="35"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="31"/>
       <c r="C229" s="6"/>
       <c r="D229" s="5"/>
       <c r="E229" s="4"/>
-      <c r="F229" s="33"/>
+      <c r="F229" s="29"/>
     </row>
     <row r="230" spans="1:6">
-      <c r="A230" s="34"/>
-      <c r="B230" s="35"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="31"/>
       <c r="C230" s="6"/>
       <c r="D230" s="5"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="33"/>
+      <c r="F230" s="29"/>
     </row>
     <row r="231" spans="1:6">
-      <c r="A231" s="36"/>
-      <c r="B231" s="37"/>
+      <c r="A231" s="32"/>
+      <c r="B231" s="33"/>
       <c r="C231" s="6"/>
       <c r="D231" s="5"/>
       <c r="E231" s="4"/>
-      <c r="F231" s="33"/>
+      <c r="F231" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5933,6 +5935,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6076,34 +6093,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -6117,4 +6107,16 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
--- a/ID7010_E22.xlsx
+++ b/ID7010_E22.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS-2024-2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7534444A-FC26-4D7A-BDE0-F97892B15E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CE929E-77BD-4208-9E3C-24BED51955F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="383">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1166,6 +1166,9 @@
   </si>
   <si>
     <t>2018/E/086</t>
+  </si>
+  <si>
+    <t>2021/E/115</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1424,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1520,6 +1523,9 @@
     </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -1810,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="23" customWidth="1"/>
@@ -5301,200 +5307,194 @@
       </c>
     </row>
     <row r="175" spans="1:6">
-      <c r="A175" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="C175" s="20">
-        <v>78</v>
-      </c>
-      <c r="D175" s="37">
-        <v>91</v>
-      </c>
-      <c r="E175" s="20">
-        <v>57</v>
-      </c>
-      <c r="F175" s="36">
-        <v>85.71</v>
-      </c>
+      <c r="A175" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B175" s="8"/>
+      <c r="C175" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D175" s="37"/>
+      <c r="E175" s="39">
+        <v>73</v>
+      </c>
+      <c r="F175" s="36"/>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="14" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C176" s="20">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D176" s="37">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E176" s="20">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F176" s="36">
-        <v>66.67</v>
+        <v>85.71</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="14" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C177" s="20">
-        <v>80</v>
-      </c>
-      <c r="D177" s="38">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="D177" s="37">
+        <v>85</v>
       </c>
       <c r="E177" s="20">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F177" s="36">
-        <v>76.19</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="14" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C178" s="20">
-        <v>50</v>
-      </c>
-      <c r="D178" s="37">
-        <v>91</v>
+        <v>80</v>
+      </c>
+      <c r="D178" s="38">
+        <v>78</v>
       </c>
       <c r="E178" s="20">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F178" s="36">
-        <v>90.48</v>
+        <v>76.19</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="14" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C179" s="20">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D179" s="37">
         <v>91</v>
       </c>
       <c r="E179" s="20">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F179" s="36">
-        <v>85.71</v>
+        <v>90.48</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="14" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C180" s="20">
         <v>80</v>
       </c>
       <c r="D180" s="37">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E180" s="20">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F180" s="36">
-        <v>76.19</v>
+        <v>85.71</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="14" t="s">
-        <v>7</v>
+        <v>335</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C181" s="20">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D181" s="37">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E181" s="20">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F181" s="36">
-        <v>71.430000000000007</v>
+        <v>76.19</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="14" t="s">
-        <v>336</v>
+        <v>7</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C182" s="20">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="D182" s="37">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E182" s="20">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F182" s="36">
-        <v>76.19</v>
+        <v>71.430000000000007</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="C183" s="20">
-        <v>87</v>
-      </c>
-      <c r="D183" s="38">
-        <v>80</v>
+        <v>85</v>
+      </c>
+      <c r="D183" s="37">
+        <v>85</v>
       </c>
       <c r="E183" s="20">
-        <v>57</v>
-      </c>
-      <c r="F183" s="35">
-        <v>80.95</v>
+        <v>52</v>
+      </c>
+      <c r="F183" s="36">
+        <v>76.19</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="14" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C184" s="20">
-        <v>85</v>
-      </c>
-      <c r="D184" s="37">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="D184" s="38">
+        <v>80</v>
       </c>
       <c r="E184" s="20">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F184" s="35">
         <v>80.95</v>
@@ -5502,85 +5502,91 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="14" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="C185" s="20">
         <v>85</v>
       </c>
       <c r="D185" s="37">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E185" s="20">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F185" s="35">
         <v>80.95</v>
       </c>
     </row>
     <row r="186" spans="1:6">
-      <c r="A186" s="22" t="s">
-        <v>372</v>
-      </c>
-      <c r="B186" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="C186" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D186" s="37"/>
+      <c r="A186" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C186" s="20">
+        <v>85</v>
+      </c>
+      <c r="D186" s="37">
+        <v>80</v>
+      </c>
       <c r="E186" s="20">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F186" s="35">
-        <v>38.1</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="22" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B187" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="C187" s="20">
-        <v>80</v>
-      </c>
-      <c r="D187" s="37">
-        <v>80</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="C187" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D187" s="37"/>
       <c r="E187" s="20">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="F187" s="35">
-        <v>44.440000000000005</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="B188" s="21"/>
-      <c r="C188" s="20"/>
-      <c r="D188" s="37"/>
+        <v>374</v>
+      </c>
+      <c r="B188" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="C188" s="20">
+        <v>80</v>
+      </c>
+      <c r="D188" s="37">
+        <v>80</v>
+      </c>
       <c r="E188" s="20">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F188" s="35">
-        <v>0</v>
+        <v>44.440000000000005</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="22" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B189" s="21"/>
       <c r="C189" s="20"/>
       <c r="D189" s="37"/>
       <c r="E189" s="20">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="F189" s="35">
         <v>0</v>
@@ -5588,25 +5594,31 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B190" s="21"/>
       <c r="C190" s="20"/>
       <c r="D190" s="37"/>
       <c r="E190" s="20">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F190" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="A191" s="24"/>
-      <c r="B191" s="25"/>
-      <c r="C191" s="4"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="4"/>
-      <c r="F191" s="29"/>
+      <c r="A191" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="B191" s="21"/>
+      <c r="C191" s="20"/>
+      <c r="D191" s="37"/>
+      <c r="E191" s="20">
+        <v>31</v>
+      </c>
+      <c r="F191" s="35">
+        <v>0</v>
+      </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="24"/>
@@ -5617,7 +5629,7 @@
       <c r="F192" s="29"/>
     </row>
     <row r="193" spans="1:6">
-      <c r="A193" s="26"/>
+      <c r="A193" s="24"/>
       <c r="B193" s="25"/>
       <c r="C193" s="4"/>
       <c r="D193" s="5"/>
@@ -5633,9 +5645,9 @@
       <c r="F194" s="29"/>
     </row>
     <row r="195" spans="1:6">
-      <c r="A195" s="24"/>
+      <c r="A195" s="26"/>
       <c r="B195" s="25"/>
-      <c r="C195" s="6"/>
+      <c r="C195" s="4"/>
       <c r="D195" s="5"/>
       <c r="E195" s="4"/>
       <c r="F195" s="29"/>
@@ -5681,8 +5693,8 @@
       <c r="F200" s="29"/>
     </row>
     <row r="201" spans="1:6">
-      <c r="A201" s="27"/>
-      <c r="B201" s="28"/>
+      <c r="A201" s="24"/>
+      <c r="B201" s="25"/>
       <c r="C201" s="6"/>
       <c r="D201" s="5"/>
       <c r="E201" s="4"/>
@@ -5889,8 +5901,8 @@
       <c r="F226" s="29"/>
     </row>
     <row r="227" spans="1:6">
-      <c r="A227" s="30"/>
-      <c r="B227" s="31"/>
+      <c r="A227" s="27"/>
+      <c r="B227" s="28"/>
       <c r="C227" s="6"/>
       <c r="D227" s="5"/>
       <c r="E227" s="4"/>
@@ -5921,12 +5933,20 @@
       <c r="F230" s="29"/>
     </row>
     <row r="231" spans="1:6">
-      <c r="A231" s="32"/>
-      <c r="B231" s="33"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="31"/>
       <c r="C231" s="6"/>
       <c r="D231" s="5"/>
       <c r="E231" s="4"/>
       <c r="F231" s="29"/>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="32"/>
+      <c r="B232" s="33"/>
+      <c r="C232" s="6"/>
+      <c r="D232" s="5"/>
+      <c r="E232" s="4"/>
+      <c r="F232" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5941,15 +5961,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6093,6 +6104,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
@@ -6110,13 +6130,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>